--- a/output/industry_limit_up_stats_20d.xlsx
+++ b/output/industry_limit_up_stats_20d.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="330">
   <si>
     <t>L1_Industry</t>
   </si>
@@ -67,10 +67,16 @@
     <t>汽车</t>
   </si>
   <si>
+    <t>轻工制造</t>
+  </si>
+  <si>
     <t>建筑装饰</t>
   </si>
   <si>
-    <t>轻工制造</t>
+    <t>环保</t>
+  </si>
+  <si>
+    <t>房地产</t>
   </si>
   <si>
     <t>医药生物</t>
@@ -79,15 +85,9 @@
     <t>国防军工</t>
   </si>
   <si>
-    <t>房地产</t>
-  </si>
-  <si>
     <t>农林牧渔</t>
   </si>
   <si>
-    <t>环保</t>
-  </si>
-  <si>
     <t>有色金属</t>
   </si>
   <si>
@@ -97,30 +97,30 @@
     <t>非银金融</t>
   </si>
   <si>
+    <t>纺织服饰</t>
+  </si>
+  <si>
     <t>钢铁</t>
   </si>
   <si>
+    <t>家用电器</t>
+  </si>
+  <si>
     <t>综合</t>
   </si>
   <si>
-    <t>家用电器</t>
-  </si>
-  <si>
-    <t>纺织服饰</t>
+    <t>传媒</t>
+  </si>
+  <si>
+    <t>食品饮料</t>
+  </si>
+  <si>
+    <t>商贸零售</t>
   </si>
   <si>
     <t>建筑材料</t>
   </si>
   <si>
-    <t>传媒</t>
-  </si>
-  <si>
-    <t>商贸零售</t>
-  </si>
-  <si>
-    <t>食品饮料</t>
-  </si>
-  <si>
     <t>社会服务</t>
   </si>
   <si>
@@ -133,55 +133,67 @@
     <t>通用设备</t>
   </si>
   <si>
+    <t>光学光电子</t>
+  </si>
+  <si>
     <t>专用设备</t>
   </si>
   <si>
-    <t>光学光电子</t>
-  </si>
-  <si>
     <t>化学原料</t>
   </si>
   <si>
+    <t>油服工程</t>
+  </si>
+  <si>
     <t>燃气Ⅱ</t>
   </si>
   <si>
-    <t>油服工程</t>
+    <t>通信设备</t>
+  </si>
+  <si>
+    <t>光伏设备</t>
+  </si>
+  <si>
+    <t>元件</t>
   </si>
   <si>
     <t>炼化及贸易</t>
   </si>
   <si>
-    <t>通信设备</t>
-  </si>
-  <si>
     <t>IT服务Ⅱ</t>
   </si>
   <si>
-    <t>元件</t>
-  </si>
-  <si>
-    <t>光伏设备</t>
-  </si>
-  <si>
     <t>农化制品</t>
   </si>
   <si>
+    <t>航运港口</t>
+  </si>
+  <si>
+    <t>化学制品</t>
+  </si>
+  <si>
+    <t>汽车零部件</t>
+  </si>
+  <si>
     <t>化学纤维</t>
   </si>
   <si>
-    <t>化学制品</t>
-  </si>
-  <si>
-    <t>航运港口</t>
-  </si>
-  <si>
-    <t>汽车零部件</t>
+    <t>包装印刷</t>
   </si>
   <si>
     <t>基础建设</t>
   </si>
   <si>
-    <t>包装印刷</t>
+    <t>家居用品</t>
+  </si>
+  <si>
+    <t>专业工程</t>
+  </si>
+  <si>
+    <t>环境治理</t>
+  </si>
+  <si>
+    <t>房地产开发</t>
   </si>
   <si>
     <t>风电设备</t>
@@ -190,156 +202,177 @@
     <t>医疗器械</t>
   </si>
   <si>
-    <t>家居用品</t>
+    <t>化学制药</t>
   </si>
   <si>
     <t>消费电子</t>
   </si>
   <si>
-    <t>专业工程</t>
+    <t>计算机设备</t>
   </si>
   <si>
     <t>军工电子Ⅱ</t>
   </si>
   <si>
-    <t>房地产开发</t>
-  </si>
-  <si>
-    <t>计算机设备</t>
+    <t>通信服务</t>
   </si>
   <si>
     <t>种植业</t>
   </si>
   <si>
-    <t>化学制药</t>
-  </si>
-  <si>
     <t>油气开采Ⅱ</t>
   </si>
   <si>
-    <t>通信服务</t>
-  </si>
-  <si>
     <t>软件开发</t>
   </si>
   <si>
-    <t>环境治理</t>
+    <t>其他电源设备Ⅱ</t>
+  </si>
+  <si>
+    <t>小金属</t>
   </si>
   <si>
     <t>电池</t>
   </si>
   <si>
-    <t>其他电源设备Ⅱ</t>
+    <t>环保设备Ⅱ</t>
   </si>
   <si>
     <t>贵金属</t>
   </si>
   <si>
-    <t>小金属</t>
-  </si>
-  <si>
-    <t>环保设备Ⅱ</t>
+    <t>塑料</t>
   </si>
   <si>
     <t>造纸</t>
   </si>
   <si>
+    <t>焦炭Ⅱ</t>
+  </si>
+  <si>
+    <t>煤炭开采</t>
+  </si>
+  <si>
+    <t>多元金融</t>
+  </si>
+  <si>
+    <t>工程机械</t>
+  </si>
+  <si>
+    <t>文娱用品</t>
+  </si>
+  <si>
+    <t>其他电子Ⅱ</t>
+  </si>
+  <si>
     <t>物流</t>
   </si>
   <si>
-    <t>塑料</t>
-  </si>
-  <si>
-    <t>其他电子Ⅱ</t>
-  </si>
-  <si>
-    <t>焦炭Ⅱ</t>
-  </si>
-  <si>
-    <t>多元金融</t>
-  </si>
-  <si>
-    <t>文娱用品</t>
-  </si>
-  <si>
-    <t>工程机械</t>
+    <t>地面兵装Ⅱ</t>
+  </si>
+  <si>
+    <t>纺织制造</t>
   </si>
   <si>
     <t>半导体</t>
   </si>
   <si>
+    <t>房屋建设Ⅱ</t>
+  </si>
+  <si>
     <t>普钢</t>
   </si>
   <si>
-    <t>煤炭开采</t>
-  </si>
-  <si>
-    <t>房屋建设Ⅱ</t>
+    <t>冶钢原料</t>
+  </si>
+  <si>
+    <t>电机Ⅱ</t>
+  </si>
+  <si>
+    <t>工业金属</t>
+  </si>
+  <si>
+    <t>工程咨询服务Ⅱ</t>
+  </si>
+  <si>
+    <t>服装家纺</t>
+  </si>
+  <si>
+    <t>装修装饰Ⅱ</t>
+  </si>
+  <si>
+    <t>厨卫电器</t>
+  </si>
+  <si>
+    <t>综合Ⅱ</t>
+  </si>
+  <si>
+    <t>出版</t>
   </si>
   <si>
     <t>生物制品</t>
   </si>
   <si>
-    <t>冶钢原料</t>
-  </si>
-  <si>
-    <t>综合Ⅱ</t>
-  </si>
-  <si>
-    <t>厨卫电器</t>
-  </si>
-  <si>
-    <t>电机Ⅱ</t>
-  </si>
-  <si>
-    <t>工程咨询服务Ⅱ</t>
-  </si>
-  <si>
-    <t>纺织制造</t>
+    <t>非金属材料Ⅱ</t>
+  </si>
+  <si>
+    <t>调味发酵品Ⅱ</t>
+  </si>
+  <si>
+    <t>橡胶</t>
+  </si>
+  <si>
+    <t>航空装备Ⅱ</t>
+  </si>
+  <si>
+    <t>一般零售</t>
+  </si>
+  <si>
+    <t>黑色家电</t>
+  </si>
+  <si>
+    <t>家电零部件Ⅱ</t>
+  </si>
+  <si>
+    <t>摩托车及其他</t>
+  </si>
+  <si>
+    <t>水泥</t>
+  </si>
+  <si>
+    <t>金属新材料</t>
   </si>
   <si>
     <t>装修建材</t>
   </si>
   <si>
-    <t>出版</t>
-  </si>
-  <si>
     <t>照明设备Ⅱ</t>
   </si>
   <si>
-    <t>装修装饰Ⅱ</t>
-  </si>
-  <si>
-    <t>家电零部件Ⅱ</t>
-  </si>
-  <si>
-    <t>服装家纺</t>
-  </si>
-  <si>
-    <t>航空装备Ⅱ</t>
-  </si>
-  <si>
-    <t>金属新材料</t>
-  </si>
-  <si>
-    <t>橡胶</t>
-  </si>
-  <si>
-    <t>非金属材料Ⅱ</t>
-  </si>
-  <si>
-    <t>黑色家电</t>
-  </si>
-  <si>
-    <t>一般零售</t>
-  </si>
-  <si>
-    <t>调味发酵品Ⅱ</t>
+    <t>互联网电商</t>
+  </si>
+  <si>
+    <t>能源金属</t>
   </si>
   <si>
     <t>电视广播Ⅱ</t>
   </si>
   <si>
+    <t>乘用车</t>
+  </si>
+  <si>
+    <t>养殖业</t>
+  </si>
+  <si>
+    <t>房地产服务</t>
+  </si>
+  <si>
+    <t>食品加工</t>
+  </si>
+  <si>
+    <t>电子化学品Ⅱ</t>
+  </si>
+  <si>
     <t>白色家电</t>
   </si>
   <si>
@@ -349,66 +382,42 @@
     <t>饲料</t>
   </si>
   <si>
-    <t>乘用车</t>
-  </si>
-  <si>
-    <t>养殖业</t>
-  </si>
-  <si>
-    <t>房地产服务</t>
-  </si>
-  <si>
-    <t>食品加工</t>
+    <t>小家电</t>
   </si>
   <si>
     <t>游戏Ⅱ</t>
   </si>
   <si>
-    <t>电子化学品Ⅱ</t>
-  </si>
-  <si>
-    <t>工业金属</t>
-  </si>
-  <si>
     <t>医疗服务</t>
   </si>
   <si>
+    <t>医药商业</t>
+  </si>
+  <si>
+    <t>教育</t>
+  </si>
+  <si>
+    <t>特钢Ⅱ</t>
+  </si>
+  <si>
     <t>汽车服务</t>
   </si>
   <si>
-    <t>特钢Ⅱ</t>
-  </si>
-  <si>
-    <t>小家电</t>
-  </si>
-  <si>
-    <t>医药商业</t>
-  </si>
-  <si>
     <t>轨交设备Ⅱ</t>
   </si>
   <si>
-    <t>教育</t>
+    <t>铁路公路</t>
   </si>
   <si>
     <t>自动化设备</t>
   </si>
   <si>
-    <t>铁路公路</t>
-  </si>
-  <si>
-    <t>水泥</t>
-  </si>
-  <si>
     <t>中药Ⅱ</t>
   </si>
   <si>
     <t>航天装备Ⅱ</t>
   </si>
   <si>
-    <t>地面兵装Ⅱ</t>
-  </si>
-  <si>
     <t>火力发电</t>
   </si>
   <si>
@@ -418,55 +427,67 @@
     <t>机床工具</t>
   </si>
   <si>
+    <t>面板</t>
+  </si>
+  <si>
     <t>能源及重型设备</t>
   </si>
   <si>
-    <t>面板</t>
-  </si>
-  <si>
     <t>纯碱</t>
   </si>
   <si>
+    <t>油田服务</t>
+  </si>
+  <si>
     <t>燃气Ⅲ</t>
   </si>
   <si>
-    <t>油田服务</t>
+    <t>通信网络设备及器件</t>
+  </si>
+  <si>
+    <t>硅料硅片</t>
+  </si>
+  <si>
+    <t>印制电路板</t>
   </si>
   <si>
     <t>炼油化工</t>
   </si>
   <si>
-    <t>通信网络设备及器件</t>
-  </si>
-  <si>
     <t>IT服务Ⅲ</t>
   </si>
   <si>
-    <t>印制电路板</t>
-  </si>
-  <si>
-    <t>硅料硅片</t>
-  </si>
-  <si>
     <t>氮肥</t>
   </si>
   <si>
+    <t>航运</t>
+  </si>
+  <si>
+    <t>涂料油墨</t>
+  </si>
+  <si>
+    <t>车身附件及饰件</t>
+  </si>
+  <si>
     <t>涤纶</t>
   </si>
   <si>
-    <t>涂料油墨</t>
-  </si>
-  <si>
-    <t>航运</t>
-  </si>
-  <si>
-    <t>车身附件及饰件</t>
+    <t>印刷</t>
   </si>
   <si>
     <t>基建市政工程</t>
   </si>
   <si>
-    <t>印刷</t>
+    <t>瓷砖地板</t>
+  </si>
+  <si>
+    <t>钢结构</t>
+  </si>
+  <si>
+    <t>大气治理</t>
+  </si>
+  <si>
+    <t>住宅开发</t>
   </si>
   <si>
     <t>风电整机</t>
@@ -475,156 +496,177 @@
     <t>医疗设备</t>
   </si>
   <si>
-    <t>瓷砖地板</t>
+    <t>原料药</t>
   </si>
   <si>
     <t>品牌消费电子</t>
   </si>
   <si>
-    <t>钢结构</t>
+    <t>安防设备</t>
   </si>
   <si>
     <t>军工电子Ⅲ</t>
   </si>
   <si>
-    <t>住宅开发</t>
-  </si>
-  <si>
-    <t>安防设备</t>
+    <t>电信运营商</t>
   </si>
   <si>
     <t>种子</t>
   </si>
   <si>
-    <t>原料药</t>
-  </si>
-  <si>
     <t>油气开采Ⅲ</t>
   </si>
   <si>
-    <t>电信运营商</t>
-  </si>
-  <si>
     <t>垂直应用软件</t>
   </si>
   <si>
-    <t>大气治理</t>
+    <t>综合电力设备商</t>
+  </si>
+  <si>
+    <t>稀土</t>
   </si>
   <si>
     <t>锂电池</t>
   </si>
   <si>
-    <t>综合电力设备商</t>
+    <t>环保设备Ⅲ</t>
   </si>
   <si>
     <t>黄金</t>
   </si>
   <si>
-    <t>稀土</t>
-  </si>
-  <si>
-    <t>环保设备Ⅲ</t>
+    <t>其他塑料制品</t>
   </si>
   <si>
     <t>大宗用纸</t>
   </si>
   <si>
+    <t>焦炭Ⅲ</t>
+  </si>
+  <si>
+    <t>动力煤</t>
+  </si>
+  <si>
+    <t>金融控股</t>
+  </si>
+  <si>
+    <t>工程机械整机</t>
+  </si>
+  <si>
+    <t>文化用品</t>
+  </si>
+  <si>
+    <t>其他电子Ⅲ</t>
+  </si>
+  <si>
     <t>原材料供应链服务</t>
   </si>
   <si>
-    <t>其他塑料制品</t>
-  </si>
-  <si>
-    <t>其他电子Ⅲ</t>
-  </si>
-  <si>
-    <t>焦炭Ⅲ</t>
-  </si>
-  <si>
-    <t>金融控股</t>
-  </si>
-  <si>
-    <t>文化用品</t>
-  </si>
-  <si>
-    <t>工程机械整机</t>
+    <t>地面兵装Ⅲ</t>
+  </si>
+  <si>
+    <t>棉纺</t>
   </si>
   <si>
     <t>分立器件</t>
   </si>
   <si>
+    <t>房屋建设Ⅲ</t>
+  </si>
+  <si>
     <t>长材</t>
   </si>
   <si>
-    <t>动力煤</t>
-  </si>
-  <si>
-    <t>房屋建设Ⅲ</t>
+    <t>铁矿石</t>
+  </si>
+  <si>
+    <t>电机Ⅲ</t>
+  </si>
+  <si>
+    <t>铝</t>
+  </si>
+  <si>
+    <t>工程咨询服务Ⅲ</t>
+  </si>
+  <si>
+    <t>鞋帽及其他</t>
+  </si>
+  <si>
+    <t>装修装饰Ⅲ</t>
+  </si>
+  <si>
+    <t>厨房电器</t>
+  </si>
+  <si>
+    <t>综合Ⅲ</t>
+  </si>
+  <si>
+    <t>大众出版</t>
   </si>
   <si>
     <t>血液制品</t>
   </si>
   <si>
-    <t>铁矿石</t>
-  </si>
-  <si>
-    <t>综合Ⅲ</t>
-  </si>
-  <si>
-    <t>厨房电器</t>
-  </si>
-  <si>
-    <t>电机Ⅲ</t>
-  </si>
-  <si>
-    <t>工程咨询服务Ⅲ</t>
-  </si>
-  <si>
-    <t>棉纺</t>
+    <t>非金属材料Ⅲ</t>
+  </si>
+  <si>
+    <t>调味发酵品Ⅲ</t>
+  </si>
+  <si>
+    <t>其他橡胶制品</t>
+  </si>
+  <si>
+    <t>航空装备Ⅲ</t>
+  </si>
+  <si>
+    <t>百货</t>
+  </si>
+  <si>
+    <t>彩电</t>
+  </si>
+  <si>
+    <t>家电零部件Ⅲ</t>
+  </si>
+  <si>
+    <t>其他运输设备</t>
+  </si>
+  <si>
+    <t>水泥制造</t>
+  </si>
+  <si>
+    <t>其他金属新材料</t>
   </si>
   <si>
     <t>耐火材料</t>
   </si>
   <si>
-    <t>大众出版</t>
-  </si>
-  <si>
     <t>照明设备Ⅲ</t>
   </si>
   <si>
-    <t>装修装饰Ⅲ</t>
-  </si>
-  <si>
-    <t>家电零部件Ⅲ</t>
-  </si>
-  <si>
-    <t>鞋帽及其他</t>
-  </si>
-  <si>
-    <t>航空装备Ⅲ</t>
-  </si>
-  <si>
-    <t>其他金属新材料</t>
-  </si>
-  <si>
-    <t>其他橡胶制品</t>
-  </si>
-  <si>
-    <t>非金属材料Ⅲ</t>
-  </si>
-  <si>
-    <t>彩电</t>
-  </si>
-  <si>
-    <t>百货</t>
-  </si>
-  <si>
-    <t>调味发酵品Ⅲ</t>
+    <t>综合电商</t>
+  </si>
+  <si>
+    <t>钴</t>
   </si>
   <si>
     <t>电视广播Ⅲ</t>
   </si>
   <si>
+    <t>电动乘用车</t>
+  </si>
+  <si>
+    <t>生猪养殖</t>
+  </si>
+  <si>
+    <t>房产租赁经纪</t>
+  </si>
+  <si>
+    <t>肉制品</t>
+  </si>
+  <si>
+    <t>电子化学品Ⅲ</t>
+  </si>
+  <si>
     <t>空调</t>
   </si>
   <si>
@@ -634,282 +676,291 @@
     <t>畜禽饲料</t>
   </si>
   <si>
-    <t>电动乘用车</t>
-  </si>
-  <si>
-    <t>生猪养殖</t>
-  </si>
-  <si>
-    <t>房产租赁经纪</t>
-  </si>
-  <si>
-    <t>肉制品</t>
+    <t>厨房小家电</t>
   </si>
   <si>
     <t>游戏Ⅲ</t>
   </si>
   <si>
-    <t>电子化学品Ⅲ</t>
-  </si>
-  <si>
-    <t>铝</t>
-  </si>
-  <si>
     <t>诊断服务</t>
   </si>
   <si>
+    <t>医药流通</t>
+  </si>
+  <si>
+    <t>学历教育</t>
+  </si>
+  <si>
+    <t>特钢Ⅲ</t>
+  </si>
+  <si>
     <t>汽车经销商</t>
   </si>
   <si>
-    <t>特钢Ⅲ</t>
-  </si>
-  <si>
-    <t>厨房小家电</t>
-  </si>
-  <si>
-    <t>医药流通</t>
-  </si>
-  <si>
     <t>轨交设备Ⅲ</t>
   </si>
   <si>
-    <t>学历教育</t>
+    <t>高速公路</t>
   </si>
   <si>
     <t>机器人</t>
   </si>
   <si>
-    <t>高速公路</t>
-  </si>
-  <si>
-    <t>水泥制造</t>
-  </si>
-  <si>
     <t>中药Ⅲ</t>
   </si>
   <si>
     <t>航天装备Ⅲ</t>
   </si>
   <si>
-    <t>地面兵装Ⅲ</t>
-  </si>
-  <si>
-    <t>绿发电力,建投能源,节能风电,韶能股份,广西能源,大唐发电,华银电力,豫能控股,兆新股份,华电辽能</t>
-  </si>
-  <si>
-    <t>中超控股,汉缆股份,中电鑫龙,泽宇智能,长城科技,华通线缆,白云电器,安靠智电,起帆电缆,中国西电</t>
-  </si>
-  <si>
-    <t>宗申动力,正泰电源,凤形股份,中寰股份,海鸥股份,新柴股份,开山股份,泰嘉股份,新锦动力,大元泵业</t>
-  </si>
-  <si>
-    <t>标准股份,电光科技,展鹏科技,山东墨龙,深科达,天鹅股份,德石股份,卓郎智能,凯格精机,强瑞技术</t>
-  </si>
-  <si>
-    <t>奥瑞德,联建光电,华映科技,深纺织Ａ,晨丰科技,同兴达,纬达光电,芯瑞达,亚世光电,深华发Ａ</t>
-  </si>
-  <si>
-    <t>兴化股份,宝丰能源,江苏索普,振华股份,中盐化工,中泰化学,金煤科技,航锦科技,华塑股份,诚志股份</t>
-  </si>
-  <si>
-    <t>特瑞斯,深圳燃气,水发燃气,成都燃气,佛燃能源,万憬能源,德龙汇能,百川能源,东方环宇,天壕能源</t>
-  </si>
-  <si>
-    <t>仁智股份,惠博普,海油发展,石化油服,通源石油,准油股份,博迈科,海油工程,贝肯能源,中油工程</t>
-  </si>
-  <si>
-    <t>东方盛虹,广汇能源,广聚能源,渤海化学,泰山石油,和顺石油,上海石化,中国石化,中国石油,博汇股份</t>
-  </si>
-  <si>
-    <t>长飞光纤,剑桥科技,世嘉科技,烽火通信,铭普光磁,菲菱科思,光迅科技,瑞斯康达,特发信息,天邑股份</t>
-  </si>
-  <si>
-    <t>华是科技,铜牛信息,博睿数据,南网数字,海量数据,岩山科技,美利云,优刻得-W,宏景科技,科远智慧</t>
-  </si>
-  <si>
-    <t>超颖电子,中英科技,迅捷兴,澳弘电子,奥士康,博敏电子,金安国纪,海星股份,广合科技,东山精密</t>
-  </si>
-  <si>
-    <t>上能电气,中利集团,协鑫集成,永臻股份,横店东磁,欧晶科技,琏升科技,国晟科技,首航新能,德业股份</t>
-  </si>
-  <si>
-    <t>金正大,泸天化,红太阳,和邦生物,安道麦A,潞化科技,赤天化,东方铁塔,六国化工</t>
-  </si>
-  <si>
-    <t>双欣材料,尤夫股份,中复神鹰,吉林化纤,泰和新材,恒天海龙,新乡化纤,三房巷</t>
-  </si>
-  <si>
-    <t>凌玮科技,红 宝 丽,麦加芯彩,宏柏新材,赞宇科技,江瀚新材,安迪苏,键邦股份,梅花生物,海新能科</t>
-  </si>
-  <si>
-    <t>锦江航运,招商轮船,招商南油,海航科技,中远海能,宁波远洋,宁波海运,国航远洋,南 京 港,中远海发</t>
-  </si>
-  <si>
-    <t>雪龙集团,兴民智通,飞龙股份,纳百川,固德电材,一彬科技,坤泰股份,腾龙股份,长源东谷,中原内配</t>
-  </si>
-  <si>
-    <t>汇绿生态,中国电建,誉帆科技,美丽生态,中国核建,诚邦股份,中国能建</t>
-  </si>
-  <si>
-    <t>永吉股份,金富科技,大胜达,顺灏股份,裕同科技,嘉美包装,鸿博股份,京华激光</t>
-  </si>
-  <si>
-    <t>德力佳,振江股份,双一科技,大金重工,锡华科技,禾望电气,通裕重工,吉鑫科技,天顺风能</t>
-  </si>
-  <si>
-    <t>奥美医疗,宝莱特,中红医疗,东方海洋,南卫股份,九安医疗,基蛋生物,蓝帆医疗</t>
-  </si>
-  <si>
-    <t>华瓷股份,海鸥住工,王力安防,共创草坪,松霖科技,悦心健康,茶花股份</t>
-  </si>
-  <si>
-    <t>胜利精密,绿联科技,利通电子,可川科技,科森科技,奥海科技,新亚电子</t>
-  </si>
-  <si>
-    <t>亚翔集成,森特股份,雅博股份,再升科技,利柏特,宏盛华源</t>
-  </si>
-  <si>
-    <t>泰豪科技,西测测试,航天电器,雷科防务,华如科技,新劲刚,观想科技</t>
-  </si>
-  <si>
-    <t>中洲控股,盈新发展,市北高新,沙河股份,京能置业,首开股份,京投发展</t>
-  </si>
-  <si>
-    <t>盛视科技,同有科技,朗科科技,御银股份,智微智能,中润光学,中国长城,金溢科技,觅睿科技</t>
-  </si>
-  <si>
-    <t>亚盛集团,敦煌种业,农发种业</t>
-  </si>
-  <si>
-    <t>莎普爱思,信立泰,亚虹医药-U,美诺华,万邦德,海欣股份,联环药业</t>
-  </si>
-  <si>
-    <t>蓝焰控股,洲际油气,中国海油</t>
-  </si>
-  <si>
-    <t>国安股份,中贝通信,世纪恒通,数据港,二六三,平治信息</t>
-  </si>
-  <si>
-    <t>星环科技-U,远光软件,拓维信息,云赛智联,网达软件,延华智能</t>
-  </si>
-  <si>
-    <t>大地海洋,中国天楹,绿色动力,同兴科技,华新环保,祥龙电业</t>
-  </si>
-  <si>
-    <t>豪鹏科技,万里股份,石大胜华,维科技术,雄韬股份,璞泰来</t>
-  </si>
-  <si>
-    <t>上海电气,东方电气,科华数据,金时科技,奥 特 迅,中国动力</t>
-  </si>
-  <si>
-    <t>招金黄金,湖南黄金,四川黄金,晓程科技,赤峰黄金,西部黄金</t>
-  </si>
-  <si>
-    <t>云南锗业,翔鹭钨业,东方锆业,华锡有色,中稀有色,锡业股份</t>
-  </si>
-  <si>
-    <t>法尔胜</t>
-  </si>
-  <si>
-    <t>安妮股份,荣晟环保,冠豪高新</t>
-  </si>
-  <si>
-    <t>宏川智慧,天顺股份,龙洲股份,福然德,远大控股</t>
-  </si>
-  <si>
-    <t>乐凯胶片,道明光学,佛塑科技,沃顿科技</t>
-  </si>
-  <si>
-    <t>好利科技,可立克,京泉华,深圳华强,中电港</t>
-  </si>
-  <si>
-    <t>安泰集团,陕西黑猫</t>
-  </si>
-  <si>
-    <t>瑞达期货,中油资本,爱建集团</t>
-  </si>
-  <si>
-    <t>群兴玩具,舒华体育</t>
-  </si>
-  <si>
-    <t>安徽合力,南方路机,中际联合,长龄液压</t>
-  </si>
-  <si>
-    <t>德明利,佰维存储,长光华芯,兆易创新</t>
+    <t>大唐发电,粤电力Ａ,迪森股份,江苏新能,赣能股份,拓日新能,深南电A,华光环能,华电能源,华电辽能</t>
+  </si>
+  <si>
+    <t>长城电工,新宏泰,百利电气,汉缆股份,中超控股,新能泰山,神马电力,正泰电器,三晖电气,白云电器</t>
+  </si>
+  <si>
+    <t>正泰电源,宇环数控,威星智能,宁波精达,亚威股份,新锦动力,日发精机,川润股份,海鸥股份,永和智控</t>
+  </si>
+  <si>
+    <t>华灿光电,联建光电,聚灿光电,瑞丰光电,深纺织Ａ,奥瑞德,纬达光电,晨丰科技,聚飞光电,国星光电</t>
+  </si>
+  <si>
+    <t>标准股份,卓郎智能,泰坦股份,合锻智能,凯格精机,电光科技,长江能科,神开股份,锡装股份,同力天启</t>
+  </si>
+  <si>
+    <t>三孚股份,三友化工,新疆天业,振华股份,中盐化工,金煤科技,新金路,金瑞矿业,宝丰能源,亚星化学</t>
+  </si>
+  <si>
+    <t>惠博普,准油股份,贝肯能源,中油工程,中海油服,海油工程,科力股份,通源石油,中曼石油,博迈科</t>
+  </si>
+  <si>
+    <t>大众公用,凯添燃气,深圳燃气,百川能源,东方环宇,美能能源,首华燃气,洪通燃气,胜利股份,万憬能源</t>
+  </si>
+  <si>
+    <t>鼎信通讯,长江通信,烽火通信,瑞斯康达,剑桥科技,世嘉科技,联特科技,天邑股份,特发信息,光迅科技</t>
+  </si>
+  <si>
+    <t>永臻股份,国晟科技,中利集团,琏升科技,首航新能,华民股份,协鑫集成,欧晶科技,德业股份,亿晶光电</t>
+  </si>
+  <si>
+    <t>澳弘电子,超颖电子,中英科技,海星股份,泰晶科技,迅捷兴,东山精密,金安国纪,奥士康,广合科技</t>
+  </si>
+  <si>
+    <t>和顺石油,茂化实华,上海石化,中国石化,恒逸石化,泰山石油,宇新股份,广汇能源,博汇股份,中国石油</t>
+  </si>
+  <si>
+    <t>优刻得-W,真视通,岩山科技,美利云,海量数据,南网数字,神州信息,宏景科技,科远智慧,博睿数据</t>
+  </si>
+  <si>
+    <t>金正大,泸天化,东方铁塔,安道麦A,潞化科技,红太阳,和邦生物,赤天化,六国化工</t>
+  </si>
+  <si>
+    <t>招商轮船,海航科技,南 京 港,宁波远洋,国航远洋,中远海发,中远海能,招商南油,宁波海运,锦江航运</t>
+  </si>
+  <si>
+    <t>红 宝 丽,安迪苏,海新能科,键邦股份,红墙股份,梅花生物,康达新材,晨光新材,凌玮科技,赞宇科技</t>
+  </si>
+  <si>
+    <t>腾龙股份,兴民智通,纳百川,中原内配,长源东谷,坤泰股份,金鸿顺,湖南天雁,雪龙集团,建设工业</t>
+  </si>
+  <si>
+    <t>三房巷,恒天海龙,尤夫股份,中复神鹰,吉林化纤,泰和新材,新乡化纤,双欣材料</t>
+  </si>
+  <si>
+    <t>裕同科技,顺灏股份,永吉股份,京华激光,鸿博股份,嘉美包装,康欣新材,大胜达,金富科技</t>
+  </si>
+  <si>
+    <t>汇绿生态,中国电建,誉帆科技,美丽生态,普邦股份,中国核建,诚邦股份,中国能建</t>
+  </si>
+  <si>
+    <t>共创草坪,华瓷股份,德尔未来,松霖科技,王力安防,海鸥住工,悦心健康,茶花股份,联翔股份</t>
+  </si>
+  <si>
+    <t>亚翔集成,北方国际,雅博股份,华电科工,再升科技,森特股份,利柏特,宏盛华源</t>
+  </si>
+  <si>
+    <t>同兴科技,中国天楹,海天股份,华新环保,绿色动力,祥龙电业,雪浪环境,大地海洋,绿茵生态</t>
+  </si>
+  <si>
+    <t>京能置业,中洲控股,黑牡丹,市北高新,西藏城投,盈新发展,首开股份,沙河股份,京投发展</t>
+  </si>
+  <si>
+    <t>双一科技,吉鑫科技,通裕重工,天顺风能,禾望电气,德力佳,大金重工,振江股份,锡华科技</t>
+  </si>
+  <si>
+    <t>九安医疗,中红医疗,蓝帆医疗,奥美医疗,基蛋生物,东方海洋,南卫股份,宝莱特</t>
+  </si>
+  <si>
+    <t>信立泰,亚虹医药-U,美诺华,莎普爱思,富祥药业,联环药业,万邦德,海欣股份</t>
+  </si>
+  <si>
+    <t>科森科技,新亚电子,奥海科技,杰美特,胜利精密,绿联科技,利通电子,可川科技</t>
+  </si>
+  <si>
+    <t>中国长城,中润光学,同有科技,智微智能,御银股份,金溢科技,觅睿科技,朗科科技,盛视科技</t>
+  </si>
+  <si>
+    <t>航天电器,观想科技,雷科防务,西测测试,华如科技,泰豪科技,新劲刚</t>
+  </si>
+  <si>
+    <t>二六三,亚联发展,中贝通信,平治信息,世纪恒通,国安股份,数据港</t>
+  </si>
+  <si>
+    <t>农发种业,敦煌种业,亚盛集团</t>
+  </si>
+  <si>
+    <t>中国海油,蓝焰控股,洲际油气</t>
+  </si>
+  <si>
+    <t>远光软件,星环科技-U,拓维信息,网达软件,云赛智联,延华智能</t>
+  </si>
+  <si>
+    <t>科华数据,科威尔,东方电气,金时科技,上海电气,中国动力,奥 特 迅</t>
+  </si>
+  <si>
+    <t>锡业股份,华锡有色,云南锗业,翔鹭钨业,东方锆业,中稀有色</t>
+  </si>
+  <si>
+    <t>维科技术,豪鹏科技,石大胜华,万里股份,雄韬股份,璞泰来</t>
+  </si>
+  <si>
+    <t>法尔胜,华宏科技</t>
+  </si>
+  <si>
+    <t>晓程科技,赤峰黄金,湖南黄金,招金黄金,西部黄金,四川黄金</t>
+  </si>
+  <si>
+    <t>金发科技,佛塑科技,乐凯胶片,道明光学,沃顿科技</t>
+  </si>
+  <si>
+    <t>荣晟环保,安妮股份,冠豪高新</t>
+  </si>
+  <si>
+    <t>安泰集团,陕西黑猫,云煤能源</t>
+  </si>
+  <si>
+    <t>辽宁能源,兖矿能源,郑州煤电,大有能源</t>
+  </si>
+  <si>
+    <t>爱建集团,瑞达期货,渤海租赁,中油资本</t>
+  </si>
+  <si>
+    <t>中际联合,华东重机,长龄液压,安徽合力,南方路机</t>
+  </si>
+  <si>
+    <t>舒华体育,群兴玩具</t>
+  </si>
+  <si>
+    <t>好利科技,京泉华,深圳华强,可立克,中电港</t>
+  </si>
+  <si>
+    <t>龙洲股份,远大控股,宏川智慧,天顺股份,福然德</t>
+  </si>
+  <si>
+    <t>北方导航,银河电子,光电股份,长城军工</t>
+  </si>
+  <si>
+    <t>孚日股份,健盛集团,云中马,江南高纤</t>
+  </si>
+  <si>
+    <t>兆易创新,德明利,佰维存储,长光华芯</t>
+  </si>
+  <si>
+    <t>宁波建工</t>
   </si>
   <si>
     <t>酒钢宏兴,安阳钢铁</t>
   </si>
   <si>
-    <t>郑州煤电,大有能源,兖矿能源</t>
-  </si>
-  <si>
-    <t>宁波建工</t>
-  </si>
-  <si>
-    <t>万泽股份,中源协和</t>
-  </si>
-  <si>
-    <t>海南矿业,方大炭素</t>
-  </si>
-  <si>
-    <t>南京公用,粤桂股份</t>
+    <t>大中矿业,方大炭素,海南矿业</t>
+  </si>
+  <si>
+    <t>祥明智能,八方股份,兆威机电</t>
+  </si>
+  <si>
+    <t>丽岛新材,众源新材,国城矿业</t>
+  </si>
+  <si>
+    <t>中国瑞林,中衡设计,太极实业</t>
+  </si>
+  <si>
+    <t>奥康国际,浪莎股份,歌力思,真爱美家</t>
+  </si>
+  <si>
+    <t>德才股份,科新发展</t>
   </si>
   <si>
     <t>万和电气,日出东方</t>
   </si>
   <si>
-    <t>祥明智能,兆威机电,八方股份</t>
-  </si>
-  <si>
-    <t>中衡设计,中国瑞林,太极实业</t>
-  </si>
-  <si>
-    <t>健盛集团,云中马</t>
+    <t>粤桂股份,南京公用</t>
+  </si>
+  <si>
+    <t>中国科传,新华传媒</t>
+  </si>
+  <si>
+    <t>中源协和,万泽股份</t>
+  </si>
+  <si>
+    <t>石英股份,联瑞新材</t>
+  </si>
+  <si>
+    <t>莲花控股</t>
+  </si>
+  <si>
+    <t>联科科技,黑猫股份</t>
+  </si>
+  <si>
+    <t>航天彩虹</t>
+  </si>
+  <si>
+    <t>赫美集团,茂业商业</t>
+  </si>
+  <si>
+    <t>兆驰股份</t>
+  </si>
+  <si>
+    <t>禾盛新材,金海高科</t>
+  </si>
+  <si>
+    <t>爱玛科技,新日股份</t>
+  </si>
+  <si>
+    <t>韩建河山</t>
+  </si>
+  <si>
+    <t>福达合金,深圳新星</t>
   </si>
   <si>
     <t>法狮龙,扬子新材</t>
   </si>
   <si>
-    <t>中国科传,新华传媒</t>
-  </si>
-  <si>
     <t>联域股份,海洋王</t>
   </si>
   <si>
-    <t>德才股份,科新发展</t>
-  </si>
-  <si>
-    <t>禾盛新材,金海高科</t>
-  </si>
-  <si>
-    <t>奥康国际,真爱美家</t>
-  </si>
-  <si>
-    <t>航天彩虹</t>
-  </si>
-  <si>
-    <t>福达合金,深圳新星</t>
-  </si>
-  <si>
-    <t>联科科技,黑猫股份</t>
-  </si>
-  <si>
-    <t>石英股份,联瑞新材</t>
-  </si>
-  <si>
-    <t>兆驰股份</t>
-  </si>
-  <si>
-    <t>茂业商业,赫美集团</t>
-  </si>
-  <si>
-    <t>莲花控股</t>
+    <t>狮头股份</t>
+  </si>
+  <si>
+    <t>融捷股份</t>
   </si>
   <si>
     <t>贵广网络</t>
   </si>
   <si>
+    <t>海马汽车</t>
+  </si>
+  <si>
+    <t>京基智农</t>
+  </si>
+  <si>
+    <t>世联行</t>
+  </si>
+  <si>
+    <t>西王食品</t>
+  </si>
+  <si>
+    <t>天通股份</t>
+  </si>
+  <si>
     <t>澳柯玛</t>
   </si>
   <si>
@@ -919,80 +970,48 @@
     <t>播恩集团</t>
   </si>
   <si>
-    <t>海马汽车</t>
-  </si>
-  <si>
-    <t>京基智农</t>
-  </si>
-  <si>
-    <t>世联行</t>
-  </si>
-  <si>
-    <t>西王食品</t>
+    <t>彩虹集团</t>
   </si>
   <si>
     <t>顺网科技</t>
   </si>
   <si>
-    <t>天通股份</t>
-  </si>
-  <si>
-    <t>众源新材</t>
-  </si>
-  <si>
     <t>国际医学</t>
   </si>
   <si>
+    <t>塞力医疗</t>
+  </si>
+  <si>
+    <t>行动教育</t>
+  </si>
+  <si>
+    <t>常宝股份</t>
+  </si>
+  <si>
     <t>交运股份</t>
   </si>
   <si>
-    <t>常宝股份</t>
-  </si>
-  <si>
-    <t>彩虹集团</t>
-  </si>
-  <si>
-    <t>塞力医疗</t>
-  </si>
-  <si>
     <t>必得科技</t>
   </si>
   <si>
-    <t>行动教育</t>
+    <t>富临运业</t>
   </si>
   <si>
     <t>科瑞技术</t>
   </si>
   <si>
-    <t>富临运业</t>
-  </si>
-  <si>
-    <t>韩建河山</t>
-  </si>
-  <si>
     <t>康惠股份</t>
   </si>
   <si>
     <t>中天火箭</t>
-  </si>
-  <si>
-    <t>北方导航</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1008,7 +1027,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1016,30 +1035,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1334,29 +1335,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1368,19 +1369,19 @@
         <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D2">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F2">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="G2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1391,19 +1392,19 @@
         <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D3">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="G3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1414,65 +1415,65 @@
         <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D4">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="G5" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G6" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1483,180 +1484,180 @@
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>20</v>
       </c>
       <c r="F7">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D9">
         <v>31</v>
       </c>
       <c r="E9">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F9">
         <v>1.55</v>
       </c>
       <c r="G9" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G10" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="G11" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F12">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="G12" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D13">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F13">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="G13" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F14">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1667,7 +1668,7 @@
         <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D15">
         <v>18</v>
@@ -1679,30 +1680,30 @@
         <v>0.9</v>
       </c>
       <c r="G15" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G16" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1713,65 +1714,65 @@
         <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17">
         <v>14</v>
       </c>
       <c r="F17">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G17" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D18">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F18">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="G18" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
         <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E19">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F19">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="G19" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1782,19 +1783,19 @@
         <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D20">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F20">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G20" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1805,157 +1806,157 @@
         <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D21">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E21">
         <v>8</v>
       </c>
       <c r="F21">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="G21" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
         <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22">
         <v>9</v>
       </c>
       <c r="F22">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="G22" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
         <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E23">
         <v>8</v>
       </c>
       <c r="F23">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G23" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
         <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F24">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="G24" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
         <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="G25" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
         <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F26">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="G26" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
         <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G27" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1966,168 +1967,168 @@
         <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F28">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G28" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
         <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D29">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G29" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
         <v>64</v>
       </c>
       <c r="C30" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D30">
+        <v>10</v>
+      </c>
+      <c r="E30">
         <v>9</v>
       </c>
-      <c r="E30">
-        <v>3</v>
-      </c>
       <c r="F30">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="G30" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
         <v>65</v>
       </c>
       <c r="C31" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31">
         <v>7</v>
       </c>
       <c r="F31">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="G31" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
         <v>66</v>
       </c>
       <c r="C32" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F32">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G32" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
         <v>67</v>
       </c>
       <c r="C33" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E33">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G33" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
         <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D34">
         <v>8</v>
       </c>
       <c r="E34">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F34">
         <v>0.4</v>
       </c>
       <c r="G34" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B35" t="s">
         <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D35">
         <v>8</v>
@@ -2139,7 +2140,7 @@
         <v>0.4</v>
       </c>
       <c r="G35" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2150,433 +2151,433 @@
         <v>70</v>
       </c>
       <c r="C36" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D36">
         <v>7</v>
       </c>
       <c r="E36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36">
         <v>0.35</v>
       </c>
       <c r="G36" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B37" t="s">
         <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37">
         <v>6</v>
       </c>
       <c r="F37">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G37" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B38" t="s">
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E38">
         <v>6</v>
       </c>
       <c r="F38">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G38" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
         <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G39" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
         <v>74</v>
       </c>
       <c r="C40" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D40">
         <v>6</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F40">
         <v>0.3</v>
       </c>
       <c r="G40" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
         <v>75</v>
       </c>
       <c r="C41" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41">
         <v>5</v>
       </c>
-      <c r="E41">
-        <v>3</v>
-      </c>
       <c r="F41">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G41" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
         <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G42" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B43" t="s">
         <v>77</v>
       </c>
       <c r="C43" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F43">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G43" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
         <v>78</v>
       </c>
       <c r="C44" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F44">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G44" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B45" t="s">
         <v>79</v>
       </c>
       <c r="C45" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D45">
         <v>5</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F45">
         <v>0.25</v>
       </c>
       <c r="G45" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B46" t="s">
         <v>80</v>
       </c>
       <c r="C46" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F46">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G46" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
         <v>81</v>
       </c>
       <c r="C47" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47">
         <v>2</v>
       </c>
       <c r="F47">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G47" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B48" t="s">
         <v>82</v>
       </c>
       <c r="C48" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F48">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G48" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B49" t="s">
         <v>83</v>
       </c>
       <c r="C49" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F49">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G49" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B50" t="s">
         <v>84</v>
       </c>
       <c r="C50" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D50">
         <v>4</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F50">
         <v>0.2</v>
       </c>
       <c r="G50" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
         <v>85</v>
       </c>
       <c r="C51" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D51">
         <v>4</v>
       </c>
       <c r="E51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F51">
         <v>0.2</v>
       </c>
       <c r="G51" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B52" t="s">
         <v>86</v>
       </c>
       <c r="C52" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D52">
         <v>4</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F52">
         <v>0.2</v>
       </c>
       <c r="G52" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B53" t="s">
         <v>87</v>
       </c>
       <c r="C53" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G53" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B54" t="s">
         <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54">
         <v>2</v>
       </c>
       <c r="F54">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G54" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2587,237 +2588,237 @@
         <v>89</v>
       </c>
       <c r="C55" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="E55">
         <v>3</v>
       </c>
-      <c r="E55">
-        <v>2</v>
-      </c>
       <c r="F55">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G55" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B56" t="s">
         <v>90</v>
       </c>
       <c r="C56" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D56">
+        <v>4</v>
+      </c>
+      <c r="E56">
         <v>3</v>
       </c>
-      <c r="E56">
-        <v>2</v>
-      </c>
       <c r="F56">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G56" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B57" t="s">
         <v>91</v>
       </c>
       <c r="C57" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57">
         <v>3</v>
       </c>
       <c r="F57">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G57" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B58" t="s">
         <v>92</v>
       </c>
       <c r="C58" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58">
         <v>3</v>
       </c>
       <c r="F58">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G58" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B59" t="s">
         <v>93</v>
       </c>
       <c r="C59" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G59" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B60" t="s">
         <v>94</v>
       </c>
       <c r="C60" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60">
         <v>2</v>
       </c>
       <c r="F60">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G60" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B61" t="s">
         <v>95</v>
       </c>
       <c r="C61" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61">
         <v>2</v>
       </c>
       <c r="F61">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G61" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s">
         <v>96</v>
       </c>
       <c r="C62" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62">
         <v>2</v>
       </c>
       <c r="F62">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G62" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B63" t="s">
         <v>97</v>
       </c>
       <c r="C63" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63">
         <v>2</v>
       </c>
       <c r="F63">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G63" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
         <v>98</v>
       </c>
       <c r="C64" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64">
         <v>2</v>
       </c>
       <c r="F64">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G64" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B65" t="s">
         <v>99</v>
       </c>
       <c r="C65" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -2829,18 +2830,18 @@
         <v>0.1</v>
       </c>
       <c r="G65" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B66" t="s">
         <v>100</v>
       </c>
       <c r="C66" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -2852,18 +2853,18 @@
         <v>0.1</v>
       </c>
       <c r="G66" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B67" t="s">
         <v>101</v>
       </c>
       <c r="C67" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D67">
         <v>2</v>
@@ -2875,41 +2876,41 @@
         <v>0.1</v>
       </c>
       <c r="G67" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B68" t="s">
         <v>102</v>
       </c>
       <c r="C68" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D68">
         <v>2</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68">
         <v>0.1</v>
       </c>
       <c r="G68" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B69" t="s">
         <v>103</v>
       </c>
       <c r="C69" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -2921,7 +2922,7 @@
         <v>0.1</v>
       </c>
       <c r="G69" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2932,7 +2933,7 @@
         <v>104</v>
       </c>
       <c r="C70" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -2944,18 +2945,18 @@
         <v>0.1</v>
       </c>
       <c r="G70" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B71" t="s">
         <v>105</v>
       </c>
       <c r="C71" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -2967,133 +2968,133 @@
         <v>0.1</v>
       </c>
       <c r="G71" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B72" t="s">
         <v>106</v>
       </c>
       <c r="C72" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G72" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B73" t="s">
         <v>107</v>
       </c>
       <c r="C73" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73">
         <v>1</v>
       </c>
       <c r="F73">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G73" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B74" t="s">
         <v>108</v>
       </c>
       <c r="C74" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G74" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B75" t="s">
         <v>109</v>
       </c>
       <c r="C75" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G75" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B76" t="s">
         <v>110</v>
       </c>
       <c r="C76" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G76" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="B77" t="s">
         <v>111</v>
       </c>
       <c r="C77" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3105,18 +3106,18 @@
         <v>0.05</v>
       </c>
       <c r="G77" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B78" t="s">
         <v>112</v>
       </c>
       <c r="C78" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3128,18 +3129,18 @@
         <v>0.05</v>
       </c>
       <c r="G78" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B79" t="s">
         <v>113</v>
       </c>
       <c r="C79" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3151,18 +3152,18 @@
         <v>0.05</v>
       </c>
       <c r="G79" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B80" t="s">
         <v>114</v>
       </c>
       <c r="C80" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3174,18 +3175,18 @@
         <v>0.05</v>
       </c>
       <c r="G80" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B81" t="s">
         <v>115</v>
       </c>
       <c r="C81" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3197,18 +3198,18 @@
         <v>0.05</v>
       </c>
       <c r="G81" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B82" t="s">
         <v>116</v>
       </c>
       <c r="C82" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3220,18 +3221,18 @@
         <v>0.05</v>
       </c>
       <c r="G82" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B83" t="s">
         <v>117</v>
       </c>
       <c r="C83" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3243,18 +3244,18 @@
         <v>0.05</v>
       </c>
       <c r="G83" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B84" t="s">
         <v>118</v>
       </c>
       <c r="C84" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3266,18 +3267,18 @@
         <v>0.05</v>
       </c>
       <c r="G84" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B85" t="s">
         <v>119</v>
       </c>
       <c r="C85" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3289,18 +3290,18 @@
         <v>0.05</v>
       </c>
       <c r="G85" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B86" t="s">
         <v>120</v>
       </c>
       <c r="C86" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3312,18 +3313,18 @@
         <v>0.05</v>
       </c>
       <c r="G86" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B87" t="s">
         <v>121</v>
       </c>
       <c r="C87" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3335,18 +3336,18 @@
         <v>0.05</v>
       </c>
       <c r="G87" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B88" t="s">
         <v>122</v>
       </c>
       <c r="C88" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3358,18 +3359,18 @@
         <v>0.05</v>
       </c>
       <c r="G88" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B89" t="s">
         <v>123</v>
       </c>
       <c r="C89" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3381,18 +3382,18 @@
         <v>0.05</v>
       </c>
       <c r="G89" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B90" t="s">
         <v>124</v>
       </c>
       <c r="C90" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3404,18 +3405,18 @@
         <v>0.05</v>
       </c>
       <c r="G90" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B91" t="s">
         <v>125</v>
       </c>
       <c r="C91" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3427,18 +3428,18 @@
         <v>0.05</v>
       </c>
       <c r="G91" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B92" t="s">
         <v>126</v>
       </c>
       <c r="C92" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3450,18 +3451,18 @@
         <v>0.05</v>
       </c>
       <c r="G92" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B93" t="s">
         <v>127</v>
       </c>
       <c r="C93" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3473,18 +3474,18 @@
         <v>0.05</v>
       </c>
       <c r="G93" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B94" t="s">
         <v>128</v>
       </c>
       <c r="C94" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3496,18 +3497,18 @@
         <v>0.05</v>
       </c>
       <c r="G94" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B95" t="s">
         <v>129</v>
       </c>
       <c r="C95" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3519,18 +3520,18 @@
         <v>0.05</v>
       </c>
       <c r="G95" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B96" t="s">
         <v>130</v>
       </c>
       <c r="C96" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3542,7 +3543,76 @@
         <v>0.05</v>
       </c>
       <c r="G96" t="s">
-        <v>320</v>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>9</v>
+      </c>
+      <c r="B97" t="s">
+        <v>131</v>
+      </c>
+      <c r="C97" t="s">
+        <v>229</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97">
+        <v>0.05</v>
+      </c>
+      <c r="G97" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
+        <v>21</v>
+      </c>
+      <c r="B98" t="s">
+        <v>132</v>
+      </c>
+      <c r="C98" t="s">
+        <v>230</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98">
+        <v>0.05</v>
+      </c>
+      <c r="G98" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" t="s">
+        <v>133</v>
+      </c>
+      <c r="C99" t="s">
+        <v>231</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+      <c r="F99">
+        <v>0.05</v>
+      </c>
+      <c r="G99" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/output/industry_limit_up_stats_20d.xlsx
+++ b/output/industry_limit_up_stats_20d.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="346">
   <si>
     <t>L1_Industry</t>
   </si>
@@ -52,73 +52,76 @@
     <t>基础化工</t>
   </si>
   <si>
+    <t>通信</t>
+  </si>
+  <si>
     <t>石油石化</t>
   </si>
   <si>
-    <t>通信</t>
-  </si>
-  <si>
     <t>计算机</t>
   </si>
   <si>
+    <t>汽车</t>
+  </si>
+  <si>
+    <t>轻工制造</t>
+  </si>
+  <si>
     <t>交通运输</t>
   </si>
   <si>
-    <t>汽车</t>
-  </si>
-  <si>
-    <t>轻工制造</t>
-  </si>
-  <si>
     <t>建筑装饰</t>
   </si>
   <si>
+    <t>医药生物</t>
+  </si>
+  <si>
+    <t>房地产</t>
+  </si>
+  <si>
     <t>环保</t>
   </si>
   <si>
-    <t>房地产</t>
-  </si>
-  <si>
-    <t>医药生物</t>
-  </si>
-  <si>
     <t>国防军工</t>
   </si>
   <si>
     <t>农林牧渔</t>
   </si>
   <si>
+    <t>煤炭</t>
+  </si>
+  <si>
     <t>有色金属</t>
   </si>
   <si>
-    <t>煤炭</t>
+    <t>纺织服饰</t>
   </si>
   <si>
     <t>非银金融</t>
   </si>
   <si>
-    <t>纺织服饰</t>
+    <t>传媒</t>
   </si>
   <si>
     <t>钢铁</t>
   </si>
   <si>
+    <t>综合</t>
+  </si>
+  <si>
+    <t>建筑材料</t>
+  </si>
+  <si>
     <t>家用电器</t>
   </si>
   <si>
-    <t>综合</t>
-  </si>
-  <si>
-    <t>传媒</t>
+    <t>商贸零售</t>
   </si>
   <si>
     <t>食品饮料</t>
   </si>
   <si>
-    <t>商贸零售</t>
-  </si>
-  <si>
-    <t>建筑材料</t>
+    <t>美容护理</t>
   </si>
   <si>
     <t>社会服务</t>
@@ -133,79 +136,82 @@
     <t>通用设备</t>
   </si>
   <si>
+    <t>专用设备</t>
+  </si>
+  <si>
     <t>光学光电子</t>
   </si>
   <si>
-    <t>专用设备</t>
-  </si>
-  <si>
     <t>化学原料</t>
   </si>
   <si>
+    <t>通信设备</t>
+  </si>
+  <si>
     <t>油服工程</t>
   </si>
   <si>
     <t>燃气Ⅱ</t>
   </si>
   <si>
-    <t>通信设备</t>
-  </si>
-  <si>
     <t>光伏设备</t>
   </si>
   <si>
+    <t>IT服务Ⅱ</t>
+  </si>
+  <si>
+    <t>炼化及贸易</t>
+  </si>
+  <si>
     <t>元件</t>
   </si>
   <si>
-    <t>炼化及贸易</t>
-  </si>
-  <si>
-    <t>IT服务Ⅱ</t>
+    <t>汽车零部件</t>
+  </si>
+  <si>
+    <t>化学制品</t>
   </si>
   <si>
     <t>农化制品</t>
   </si>
   <si>
+    <t>包装印刷</t>
+  </si>
+  <si>
+    <t>化学纤维</t>
+  </si>
+  <si>
     <t>航运港口</t>
   </si>
   <si>
-    <t>化学制品</t>
-  </si>
-  <si>
-    <t>汽车零部件</t>
-  </si>
-  <si>
-    <t>化学纤维</t>
-  </si>
-  <si>
-    <t>包装印刷</t>
-  </si>
-  <si>
     <t>基础建设</t>
   </si>
   <si>
+    <t>专业工程</t>
+  </si>
+  <si>
+    <t>化学制药</t>
+  </si>
+  <si>
+    <t>消费电子</t>
+  </si>
+  <si>
     <t>家居用品</t>
   </si>
   <si>
-    <t>专业工程</t>
+    <t>房地产开发</t>
   </si>
   <si>
     <t>环境治理</t>
   </si>
   <si>
-    <t>房地产开发</t>
-  </si>
-  <si>
     <t>风电设备</t>
   </si>
   <si>
     <t>医疗器械</t>
   </si>
   <si>
-    <t>化学制药</t>
-  </si>
-  <si>
-    <t>消费电子</t>
+    <t>通信服务</t>
   </si>
   <si>
     <t>计算机设备</t>
@@ -214,198 +220,210 @@
     <t>军工电子Ⅱ</t>
   </si>
   <si>
-    <t>通信服务</t>
-  </si>
-  <si>
     <t>种植业</t>
   </si>
   <si>
+    <t>电池</t>
+  </si>
+  <si>
+    <t>软件开发</t>
+  </si>
+  <si>
     <t>油气开采Ⅱ</t>
   </si>
   <si>
-    <t>软件开发</t>
+    <t>塑料</t>
+  </si>
+  <si>
+    <t>煤炭开采</t>
+  </si>
+  <si>
+    <t>环保设备Ⅱ</t>
   </si>
   <si>
     <t>其他电源设备Ⅱ</t>
   </si>
   <si>
+    <t>造纸</t>
+  </si>
+  <si>
     <t>小金属</t>
   </si>
   <si>
-    <t>电池</t>
-  </si>
-  <si>
-    <t>环保设备Ⅱ</t>
+    <t>文娱用品</t>
+  </si>
+  <si>
+    <t>工程机械</t>
   </si>
   <si>
     <t>贵金属</t>
   </si>
   <si>
-    <t>塑料</t>
-  </si>
-  <si>
-    <t>造纸</t>
-  </si>
-  <si>
     <t>焦炭Ⅱ</t>
   </si>
   <si>
-    <t>煤炭开采</t>
+    <t>服装家纺</t>
+  </si>
+  <si>
+    <t>其他电子Ⅱ</t>
   </si>
   <si>
     <t>多元金融</t>
   </si>
   <si>
-    <t>工程机械</t>
-  </si>
-  <si>
-    <t>文娱用品</t>
-  </si>
-  <si>
-    <t>其他电子Ⅱ</t>
+    <t>半导体</t>
+  </si>
+  <si>
+    <t>地面兵装Ⅱ</t>
+  </si>
+  <si>
+    <t>纺织制造</t>
+  </si>
+  <si>
+    <t>房屋建设Ⅱ</t>
   </si>
   <si>
     <t>物流</t>
   </si>
   <si>
-    <t>地面兵装Ⅱ</t>
-  </si>
-  <si>
-    <t>纺织制造</t>
-  </si>
-  <si>
-    <t>半导体</t>
-  </si>
-  <si>
-    <t>房屋建设Ⅱ</t>
+    <t>出版</t>
   </si>
   <si>
     <t>普钢</t>
   </si>
   <si>
+    <t>电机Ⅱ</t>
+  </si>
+  <si>
+    <t>工程咨询服务Ⅱ</t>
+  </si>
+  <si>
+    <t>综合Ⅱ</t>
+  </si>
+  <si>
+    <t>工业金属</t>
+  </si>
+  <si>
     <t>冶钢原料</t>
   </si>
   <si>
-    <t>电机Ⅱ</t>
-  </si>
-  <si>
-    <t>工业金属</t>
-  </si>
-  <si>
-    <t>工程咨询服务Ⅱ</t>
-  </si>
-  <si>
-    <t>服装家纺</t>
+    <t>水泥</t>
+  </si>
+  <si>
+    <t>装修建材</t>
+  </si>
+  <si>
+    <t>厨卫电器</t>
   </si>
   <si>
     <t>装修装饰Ⅱ</t>
   </si>
   <si>
-    <t>厨卫电器</t>
-  </si>
-  <si>
-    <t>综合Ⅱ</t>
-  </si>
-  <si>
-    <t>出版</t>
+    <t>家电零部件Ⅱ</t>
   </si>
   <si>
     <t>生物制品</t>
   </si>
   <si>
+    <t>互联网电商</t>
+  </si>
+  <si>
+    <t>广告营销</t>
+  </si>
+  <si>
+    <t>能源金属</t>
+  </si>
+  <si>
+    <t>食品加工</t>
+  </si>
+  <si>
+    <t>轨交设备Ⅱ</t>
+  </si>
+  <si>
     <t>非金属材料Ⅱ</t>
   </si>
   <si>
+    <t>一般零售</t>
+  </si>
+  <si>
+    <t>照明设备Ⅱ</t>
+  </si>
+  <si>
+    <t>农产品加工</t>
+  </si>
+  <si>
+    <t>橡胶</t>
+  </si>
+  <si>
+    <t>金属新材料</t>
+  </si>
+  <si>
     <t>调味发酵品Ⅱ</t>
   </si>
   <si>
-    <t>橡胶</t>
+    <t>摩托车及其他</t>
+  </si>
+  <si>
+    <t>黑色家电</t>
   </si>
   <si>
     <t>航空装备Ⅱ</t>
   </si>
   <si>
-    <t>一般零售</t>
-  </si>
-  <si>
-    <t>黑色家电</t>
-  </si>
-  <si>
-    <t>家电零部件Ⅱ</t>
-  </si>
-  <si>
-    <t>摩托车及其他</t>
-  </si>
-  <si>
-    <t>水泥</t>
-  </si>
-  <si>
-    <t>金属新材料</t>
-  </si>
-  <si>
-    <t>装修建材</t>
-  </si>
-  <si>
-    <t>照明设备Ⅱ</t>
-  </si>
-  <si>
-    <t>互联网电商</t>
-  </si>
-  <si>
-    <t>能源金属</t>
+    <t>个护用品</t>
+  </si>
+  <si>
+    <t>旅游及景区</t>
+  </si>
+  <si>
+    <t>体育Ⅱ</t>
+  </si>
+  <si>
+    <t>林业Ⅱ</t>
   </si>
   <si>
     <t>电视广播Ⅱ</t>
   </si>
   <si>
+    <t>养殖业</t>
+  </si>
+  <si>
+    <t>电子化学品Ⅱ</t>
+  </si>
+  <si>
+    <t>白色家电</t>
+  </si>
+  <si>
+    <t>饲料</t>
+  </si>
+  <si>
+    <t>房地产服务</t>
+  </si>
+  <si>
     <t>乘用车</t>
   </si>
   <si>
-    <t>养殖业</t>
-  </si>
-  <si>
-    <t>房地产服务</t>
-  </si>
-  <si>
-    <t>食品加工</t>
-  </si>
-  <si>
-    <t>电子化学品Ⅱ</t>
-  </si>
-  <si>
-    <t>白色家电</t>
-  </si>
-  <si>
-    <t>广告营销</t>
-  </si>
-  <si>
-    <t>饲料</t>
+    <t>医药商业</t>
+  </si>
+  <si>
+    <t>游戏Ⅱ</t>
+  </si>
+  <si>
+    <t>医疗服务</t>
+  </si>
+  <si>
+    <t>特钢Ⅱ</t>
+  </si>
+  <si>
+    <t>汽车服务</t>
   </si>
   <si>
     <t>小家电</t>
   </si>
   <si>
-    <t>游戏Ⅱ</t>
-  </si>
-  <si>
-    <t>医疗服务</t>
-  </si>
-  <si>
-    <t>医药商业</t>
-  </si>
-  <si>
     <t>教育</t>
   </si>
   <si>
-    <t>特钢Ⅱ</t>
-  </si>
-  <si>
-    <t>汽车服务</t>
-  </si>
-  <si>
-    <t>轨交设备Ⅱ</t>
-  </si>
-  <si>
     <t>铁路公路</t>
   </si>
   <si>
@@ -427,79 +445,82 @@
     <t>机床工具</t>
   </si>
   <si>
+    <t>能源及重型设备</t>
+  </si>
+  <si>
     <t>面板</t>
   </si>
   <si>
-    <t>能源及重型设备</t>
-  </si>
-  <si>
     <t>纯碱</t>
   </si>
   <si>
+    <t>通信网络设备及器件</t>
+  </si>
+  <si>
     <t>油田服务</t>
   </si>
   <si>
     <t>燃气Ⅲ</t>
   </si>
   <si>
-    <t>通信网络设备及器件</t>
-  </si>
-  <si>
     <t>硅料硅片</t>
   </si>
   <si>
+    <t>IT服务Ⅲ</t>
+  </si>
+  <si>
+    <t>炼油化工</t>
+  </si>
+  <si>
     <t>印制电路板</t>
   </si>
   <si>
-    <t>炼油化工</t>
-  </si>
-  <si>
-    <t>IT服务Ⅲ</t>
+    <t>车身附件及饰件</t>
+  </si>
+  <si>
+    <t>涂料油墨</t>
   </si>
   <si>
     <t>氮肥</t>
   </si>
   <si>
+    <t>印刷</t>
+  </si>
+  <si>
+    <t>涤纶</t>
+  </si>
+  <si>
     <t>航运</t>
   </si>
   <si>
-    <t>涂料油墨</t>
-  </si>
-  <si>
-    <t>车身附件及饰件</t>
-  </si>
-  <si>
-    <t>涤纶</t>
-  </si>
-  <si>
-    <t>印刷</t>
-  </si>
-  <si>
     <t>基建市政工程</t>
   </si>
   <si>
+    <t>钢结构</t>
+  </si>
+  <si>
+    <t>原料药</t>
+  </si>
+  <si>
+    <t>品牌消费电子</t>
+  </si>
+  <si>
     <t>瓷砖地板</t>
   </si>
   <si>
-    <t>钢结构</t>
+    <t>住宅开发</t>
   </si>
   <si>
     <t>大气治理</t>
   </si>
   <si>
-    <t>住宅开发</t>
-  </si>
-  <si>
     <t>风电整机</t>
   </si>
   <si>
     <t>医疗设备</t>
   </si>
   <si>
-    <t>原料药</t>
-  </si>
-  <si>
-    <t>品牌消费电子</t>
+    <t>电信运营商</t>
   </si>
   <si>
     <t>安防设备</t>
@@ -508,198 +529,210 @@
     <t>军工电子Ⅲ</t>
   </si>
   <si>
-    <t>电信运营商</t>
-  </si>
-  <si>
     <t>种子</t>
   </si>
   <si>
+    <t>锂电池</t>
+  </si>
+  <si>
+    <t>垂直应用软件</t>
+  </si>
+  <si>
     <t>油气开采Ⅲ</t>
   </si>
   <si>
-    <t>垂直应用软件</t>
+    <t>其他塑料制品</t>
+  </si>
+  <si>
+    <t>动力煤</t>
+  </si>
+  <si>
+    <t>环保设备Ⅲ</t>
   </si>
   <si>
     <t>综合电力设备商</t>
   </si>
   <si>
+    <t>大宗用纸</t>
+  </si>
+  <si>
     <t>稀土</t>
   </si>
   <si>
-    <t>锂电池</t>
-  </si>
-  <si>
-    <t>环保设备Ⅲ</t>
+    <t>文化用品</t>
+  </si>
+  <si>
+    <t>工程机械整机</t>
   </si>
   <si>
     <t>黄金</t>
   </si>
   <si>
-    <t>其他塑料制品</t>
-  </si>
-  <si>
-    <t>大宗用纸</t>
-  </si>
-  <si>
     <t>焦炭Ⅲ</t>
   </si>
   <si>
-    <t>动力煤</t>
+    <t>鞋帽及其他</t>
+  </si>
+  <si>
+    <t>其他电子Ⅲ</t>
   </si>
   <si>
     <t>金融控股</t>
   </si>
   <si>
-    <t>工程机械整机</t>
-  </si>
-  <si>
-    <t>文化用品</t>
-  </si>
-  <si>
-    <t>其他电子Ⅲ</t>
+    <t>分立器件</t>
+  </si>
+  <si>
+    <t>地面兵装Ⅲ</t>
+  </si>
+  <si>
+    <t>棉纺</t>
+  </si>
+  <si>
+    <t>房屋建设Ⅲ</t>
   </si>
   <si>
     <t>原材料供应链服务</t>
   </si>
   <si>
-    <t>地面兵装Ⅲ</t>
-  </si>
-  <si>
-    <t>棉纺</t>
-  </si>
-  <si>
-    <t>分立器件</t>
-  </si>
-  <si>
-    <t>房屋建设Ⅲ</t>
+    <t>大众出版</t>
   </si>
   <si>
     <t>长材</t>
   </si>
   <si>
+    <t>电机Ⅲ</t>
+  </si>
+  <si>
+    <t>工程咨询服务Ⅲ</t>
+  </si>
+  <si>
+    <t>综合Ⅲ</t>
+  </si>
+  <si>
+    <t>铝</t>
+  </si>
+  <si>
     <t>铁矿石</t>
   </si>
   <si>
-    <t>电机Ⅲ</t>
-  </si>
-  <si>
-    <t>铝</t>
-  </si>
-  <si>
-    <t>工程咨询服务Ⅲ</t>
-  </si>
-  <si>
-    <t>鞋帽及其他</t>
+    <t>水泥制造</t>
+  </si>
+  <si>
+    <t>耐火材料</t>
+  </si>
+  <si>
+    <t>厨房电器</t>
   </si>
   <si>
     <t>装修装饰Ⅲ</t>
   </si>
   <si>
-    <t>厨房电器</t>
-  </si>
-  <si>
-    <t>综合Ⅲ</t>
-  </si>
-  <si>
-    <t>大众出版</t>
+    <t>家电零部件Ⅲ</t>
   </si>
   <si>
     <t>血液制品</t>
   </si>
   <si>
+    <t>综合电商</t>
+  </si>
+  <si>
+    <t>营销代理</t>
+  </si>
+  <si>
+    <t>钴</t>
+  </si>
+  <si>
+    <t>肉制品</t>
+  </si>
+  <si>
+    <t>轨交设备Ⅲ</t>
+  </si>
+  <si>
     <t>非金属材料Ⅲ</t>
   </si>
   <si>
+    <t>百货</t>
+  </si>
+  <si>
+    <t>照明设备Ⅲ</t>
+  </si>
+  <si>
+    <t>果蔬加工</t>
+  </si>
+  <si>
+    <t>其他橡胶制品</t>
+  </si>
+  <si>
+    <t>其他金属新材料</t>
+  </si>
+  <si>
     <t>调味发酵品Ⅲ</t>
   </si>
   <si>
-    <t>其他橡胶制品</t>
+    <t>其他运输设备</t>
+  </si>
+  <si>
+    <t>彩电</t>
   </si>
   <si>
     <t>航空装备Ⅲ</t>
   </si>
   <si>
-    <t>百货</t>
-  </si>
-  <si>
-    <t>彩电</t>
-  </si>
-  <si>
-    <t>家电零部件Ⅲ</t>
-  </si>
-  <si>
-    <t>其他运输设备</t>
-  </si>
-  <si>
-    <t>水泥制造</t>
-  </si>
-  <si>
-    <t>其他金属新材料</t>
-  </si>
-  <si>
-    <t>耐火材料</t>
-  </si>
-  <si>
-    <t>照明设备Ⅲ</t>
-  </si>
-  <si>
-    <t>综合电商</t>
-  </si>
-  <si>
-    <t>钴</t>
+    <t>生活用纸</t>
+  </si>
+  <si>
+    <t>人工景区</t>
+  </si>
+  <si>
+    <t>体育Ⅲ</t>
+  </si>
+  <si>
+    <t>林业Ⅲ</t>
   </si>
   <si>
     <t>电视广播Ⅲ</t>
   </si>
   <si>
+    <t>生猪养殖</t>
+  </si>
+  <si>
+    <t>电子化学品Ⅲ</t>
+  </si>
+  <si>
+    <t>空调</t>
+  </si>
+  <si>
+    <t>畜禽饲料</t>
+  </si>
+  <si>
+    <t>房产租赁经纪</t>
+  </si>
+  <si>
     <t>电动乘用车</t>
   </si>
   <si>
-    <t>生猪养殖</t>
-  </si>
-  <si>
-    <t>房产租赁经纪</t>
-  </si>
-  <si>
-    <t>肉制品</t>
-  </si>
-  <si>
-    <t>电子化学品Ⅲ</t>
-  </si>
-  <si>
-    <t>空调</t>
-  </si>
-  <si>
-    <t>营销代理</t>
-  </si>
-  <si>
-    <t>畜禽饲料</t>
+    <t>医药流通</t>
+  </si>
+  <si>
+    <t>游戏Ⅲ</t>
+  </si>
+  <si>
+    <t>诊断服务</t>
+  </si>
+  <si>
+    <t>特钢Ⅲ</t>
+  </si>
+  <si>
+    <t>汽车经销商</t>
   </si>
   <si>
     <t>厨房小家电</t>
   </si>
   <si>
-    <t>游戏Ⅲ</t>
-  </si>
-  <si>
-    <t>诊断服务</t>
-  </si>
-  <si>
-    <t>医药流通</t>
-  </si>
-  <si>
     <t>学历教育</t>
   </si>
   <si>
-    <t>特钢Ⅲ</t>
-  </si>
-  <si>
-    <t>汽车经销商</t>
-  </si>
-  <si>
-    <t>轨交设备Ⅲ</t>
-  </si>
-  <si>
     <t>高速公路</t>
   </si>
   <si>
@@ -712,286 +745,301 @@
     <t>航天装备Ⅲ</t>
   </si>
   <si>
-    <t>大唐发电,粤电力Ａ,迪森股份,江苏新能,赣能股份,拓日新能,深南电A,华光环能,华电能源,华电辽能</t>
-  </si>
-  <si>
-    <t>长城电工,新宏泰,百利电气,汉缆股份,中超控股,新能泰山,神马电力,正泰电器,三晖电气,白云电器</t>
-  </si>
-  <si>
-    <t>正泰电源,宇环数控,威星智能,宁波精达,亚威股份,新锦动力,日发精机,川润股份,海鸥股份,永和智控</t>
-  </si>
-  <si>
-    <t>华灿光电,联建光电,聚灿光电,瑞丰光电,深纺织Ａ,奥瑞德,纬达光电,晨丰科技,聚飞光电,国星光电</t>
-  </si>
-  <si>
-    <t>标准股份,卓郎智能,泰坦股份,合锻智能,凯格精机,电光科技,长江能科,神开股份,锡装股份,同力天启</t>
-  </si>
-  <si>
-    <t>三孚股份,三友化工,新疆天业,振华股份,中盐化工,金煤科技,新金路,金瑞矿业,宝丰能源,亚星化学</t>
-  </si>
-  <si>
-    <t>惠博普,准油股份,贝肯能源,中油工程,中海油服,海油工程,科力股份,通源石油,中曼石油,博迈科</t>
-  </si>
-  <si>
-    <t>大众公用,凯添燃气,深圳燃气,百川能源,东方环宇,美能能源,首华燃气,洪通燃气,胜利股份,万憬能源</t>
-  </si>
-  <si>
-    <t>鼎信通讯,长江通信,烽火通信,瑞斯康达,剑桥科技,世嘉科技,联特科技,天邑股份,特发信息,光迅科技</t>
-  </si>
-  <si>
-    <t>永臻股份,国晟科技,中利集团,琏升科技,首航新能,华民股份,协鑫集成,欧晶科技,德业股份,亿晶光电</t>
-  </si>
-  <si>
-    <t>澳弘电子,超颖电子,中英科技,海星股份,泰晶科技,迅捷兴,东山精密,金安国纪,奥士康,广合科技</t>
-  </si>
-  <si>
-    <t>和顺石油,茂化实华,上海石化,中国石化,恒逸石化,泰山石油,宇新股份,广汇能源,博汇股份,中国石油</t>
-  </si>
-  <si>
-    <t>优刻得-W,真视通,岩山科技,美利云,海量数据,南网数字,神州信息,宏景科技,科远智慧,博睿数据</t>
-  </si>
-  <si>
-    <t>金正大,泸天化,东方铁塔,安道麦A,潞化科技,红太阳,和邦生物,赤天化,六国化工</t>
-  </si>
-  <si>
-    <t>招商轮船,海航科技,南 京 港,宁波远洋,国航远洋,中远海发,中远海能,招商南油,宁波海运,锦江航运</t>
-  </si>
-  <si>
-    <t>红 宝 丽,安迪苏,海新能科,键邦股份,红墙股份,梅花生物,康达新材,晨光新材,凌玮科技,赞宇科技</t>
-  </si>
-  <si>
-    <t>腾龙股份,兴民智通,纳百川,中原内配,长源东谷,坤泰股份,金鸿顺,湖南天雁,雪龙集团,建设工业</t>
-  </si>
-  <si>
-    <t>三房巷,恒天海龙,尤夫股份,中复神鹰,吉林化纤,泰和新材,新乡化纤,双欣材料</t>
-  </si>
-  <si>
-    <t>裕同科技,顺灏股份,永吉股份,京华激光,鸿博股份,嘉美包装,康欣新材,大胜达,金富科技</t>
-  </si>
-  <si>
-    <t>汇绿生态,中国电建,誉帆科技,美丽生态,普邦股份,中国核建,诚邦股份,中国能建</t>
-  </si>
-  <si>
-    <t>共创草坪,华瓷股份,德尔未来,松霖科技,王力安防,海鸥住工,悦心健康,茶花股份,联翔股份</t>
-  </si>
-  <si>
-    <t>亚翔集成,北方国际,雅博股份,华电科工,再升科技,森特股份,利柏特,宏盛华源</t>
-  </si>
-  <si>
-    <t>同兴科技,中国天楹,海天股份,华新环保,绿色动力,祥龙电业,雪浪环境,大地海洋,绿茵生态</t>
-  </si>
-  <si>
-    <t>京能置业,中洲控股,黑牡丹,市北高新,西藏城投,盈新发展,首开股份,沙河股份,京投发展</t>
-  </si>
-  <si>
-    <t>双一科技,吉鑫科技,通裕重工,天顺风能,禾望电气,德力佳,大金重工,振江股份,锡华科技</t>
-  </si>
-  <si>
-    <t>九安医疗,中红医疗,蓝帆医疗,奥美医疗,基蛋生物,东方海洋,南卫股份,宝莱特</t>
-  </si>
-  <si>
-    <t>信立泰,亚虹医药-U,美诺华,莎普爱思,富祥药业,联环药业,万邦德,海欣股份</t>
-  </si>
-  <si>
-    <t>科森科技,新亚电子,奥海科技,杰美特,胜利精密,绿联科技,利通电子,可川科技</t>
-  </si>
-  <si>
-    <t>中国长城,中润光学,同有科技,智微智能,御银股份,金溢科技,觅睿科技,朗科科技,盛视科技</t>
-  </si>
-  <si>
-    <t>航天电器,观想科技,雷科防务,西测测试,华如科技,泰豪科技,新劲刚</t>
-  </si>
-  <si>
-    <t>二六三,亚联发展,中贝通信,平治信息,世纪恒通,国安股份,数据港</t>
+    <t>华电辽能,节能风电,通宝能源,粤电力Ａ,华电能源,闽东电力,华光环能,建投能源,晶科科技,富春环保</t>
+  </si>
+  <si>
+    <t>中国西电,汉缆股份,华盛昌,新能泰山,新宏泰,国电南自,迦南智能,三变科技,中电鑫龙,正泰电器</t>
+  </si>
+  <si>
+    <t>锋龙股份,咸亨国际,泰嘉股份,永和智控,江苏神通,新柴股份,金太阳,中寰股份,正泰电源,冰轮环境</t>
+  </si>
+  <si>
+    <t>江钨装备,神开股份,杰克科技,展鹏科技,兰石重装,长江能科,威领股份,同力天启,电光科技,锡装股份</t>
+  </si>
+  <si>
+    <t>福晶科技,冠捷科技,龙腾光电,深纺织Ａ,同兴达,聚飞光电,华映科技,瑞丰光电,亚世光电,艾比森</t>
+  </si>
+  <si>
+    <t>宝丰能源,金浦钛业,三友化工,江苏索普,振华股份,金瑞矿业,金煤科技,华塑股份,新疆天业,诚志股份</t>
+  </si>
+  <si>
+    <t>菲菱科思,鼎信通讯,长江通信,长飞光纤,烽火通信,瑞斯康达,光迅科技,阿莱德,联特科技,剑桥科技</t>
+  </si>
+  <si>
+    <t>通源石油,贝肯能源,博迈科,中曼石油,海油发展,海油工程,潜能恒信,仁智股份,准油股份,惠博普</t>
+  </si>
+  <si>
+    <t>天壕能源,洪通燃气,皖天然气,特瑞斯,德龙汇能,新疆火炬,大众公用,东方环宇,胜利股份,新天然气</t>
+  </si>
+  <si>
+    <t>华民股份,国晟科技,协鑫集成,德业股份,亿晶光电,上能电气,欧晶科技,横店东磁,中利集团,首航新能</t>
+  </si>
+  <si>
+    <t>科远智慧,美利云,宏景科技,大位科技,天玑科技,神州信息,海量数据,南网数字,博睿数据,岩山科技</t>
+  </si>
+  <si>
+    <t>宇新股份,渤海化学,博汇股份,上海石化,广聚能源,中国石油,东方盛虹,和顺石油,广汇能源,中国石化</t>
+  </si>
+  <si>
+    <t>超颖电子,博敏电子,中英科技,东山精密,金安国纪,海星股份,广合科技,澳弘电子,迅捷兴,泰晶科技</t>
+  </si>
+  <si>
+    <t>长源东谷,纳百川,湖南天雁,坤泰股份,兴民智通,金鸿顺,建设工业,腾龙股份,固德电材,雪龙集团</t>
+  </si>
+  <si>
+    <t>晨光新材,麦加芯彩,赞宇科技,海新能科,梅花生物,康达新材,百川股份,红 宝 丽,键邦股份,宏柏新材</t>
+  </si>
+  <si>
+    <t>东方铁塔,和邦生物,安道麦A,泸天化,金正大,六国化工,潞化科技,红太阳,赤天化</t>
+  </si>
+  <si>
+    <t>大胜达,顺灏股份,鸿博股份,永吉股份,珠海中富,金富科技,京华激光,裕同科技,康欣新材,嘉美包装</t>
+  </si>
+  <si>
+    <t>中复神鹰,恒天海龙,三房巷,双欣材料,新乡化纤,吉林化纤,泰和新材,尤夫股份</t>
+  </si>
+  <si>
+    <t>中远海发,中远海能,海航科技,招商南油,招商轮船,锦江航运,国航远洋,宁波远洋,宁波海运,南 京 港</t>
+  </si>
+  <si>
+    <t>美丽生态,诚邦股份,中国核建,新疆交建,誉帆科技,汇绿生态,中国能建,中国电建,普邦股份</t>
+  </si>
+  <si>
+    <t>再升科技,柏诚股份,北方国际,华电科工,利柏特,森特股份,雅博股份,亚翔集成,宏盛华源</t>
+  </si>
+  <si>
+    <t>莎普爱思,美诺华,万邦德,富祥药业,联环药业,信立泰,双鹭药业,亚虹医药-U,海欣股份</t>
+  </si>
+  <si>
+    <t>科森科技,新亚电子,胜利精密,立讯精密,利通电子,绿联科技,奥海科技,杰美特,可川科技</t>
+  </si>
+  <si>
+    <t>海鸥住工,悦心健康,茶花股份,松霖科技,共创草坪,华瓷股份,联翔股份,德尔未来,王力安防</t>
+  </si>
+  <si>
+    <t>沙河股份,黑牡丹,京投发展,市北高新,中洲控股,盈新发展,西藏城投,京能置业,首开股份</t>
+  </si>
+  <si>
+    <t>同兴科技,华新环保,绿色动力,大地海洋,海天股份,中国天楹,雪浪环境,绿茵生态,祥龙电业</t>
+  </si>
+  <si>
+    <t>德力佳,大金重工,禾望电气,锡华科技,天顺风能,振江股份,双一科技,通裕重工,吉鑫科技</t>
+  </si>
+  <si>
+    <t>九安医疗,基蛋生物,南卫股份,东方海洋,蓝帆医疗,奥美医疗,中红医疗,宝莱特</t>
+  </si>
+  <si>
+    <t>国安股份,亚联发展,世纪恒通,中嘉博创,二六三,平治信息,中贝通信,数据港</t>
+  </si>
+  <si>
+    <t>盛视科技,御银股份,觅睿科技,同有科技,金溢科技,中国长城,中润光学,智微智能,朗科科技</t>
+  </si>
+  <si>
+    <t>西测测试,观想科技,雷科防务,航天电器,华如科技,新劲刚,泰豪科技</t>
   </si>
   <si>
     <t>农发种业,敦煌种业,亚盛集团</t>
   </si>
   <si>
-    <t>中国海油,蓝焰控股,洲际油气</t>
-  </si>
-  <si>
-    <t>远光软件,星环科技-U,拓维信息,网达软件,云赛智联,延华智能</t>
-  </si>
-  <si>
-    <t>科华数据,科威尔,东方电气,金时科技,上海电气,中国动力,奥 特 迅</t>
-  </si>
-  <si>
-    <t>锡业股份,华锡有色,云南锗业,翔鹭钨业,东方锆业,中稀有色</t>
-  </si>
-  <si>
-    <t>维科技术,豪鹏科技,石大胜华,万里股份,雄韬股份,璞泰来</t>
-  </si>
-  <si>
-    <t>法尔胜,华宏科技</t>
-  </si>
-  <si>
-    <t>晓程科技,赤峰黄金,湖南黄金,招金黄金,西部黄金,四川黄金</t>
-  </si>
-  <si>
-    <t>金发科技,佛塑科技,乐凯胶片,道明光学,沃顿科技</t>
-  </si>
-  <si>
-    <t>荣晟环保,安妮股份,冠豪高新</t>
-  </si>
-  <si>
-    <t>安泰集团,陕西黑猫,云煤能源</t>
-  </si>
-  <si>
-    <t>辽宁能源,兖矿能源,郑州煤电,大有能源</t>
-  </si>
-  <si>
-    <t>爱建集团,瑞达期货,渤海租赁,中油资本</t>
-  </si>
-  <si>
-    <t>中际联合,华东重机,长龄液压,安徽合力,南方路机</t>
-  </si>
-  <si>
-    <t>舒华体育,群兴玩具</t>
-  </si>
-  <si>
-    <t>好利科技,京泉华,深圳华强,可立克,中电港</t>
-  </si>
-  <si>
-    <t>龙洲股份,远大控股,宏川智慧,天顺股份,福然德</t>
-  </si>
-  <si>
-    <t>北方导航,银河电子,光电股份,长城军工</t>
-  </si>
-  <si>
-    <t>孚日股份,健盛集团,云中马,江南高纤</t>
-  </si>
-  <si>
-    <t>兆易创新,德明利,佰维存储,长光华芯</t>
-  </si>
-  <si>
-    <t>宁波建工</t>
-  </si>
-  <si>
-    <t>酒钢宏兴,安阳钢铁</t>
-  </si>
-  <si>
-    <t>大中矿业,方大炭素,海南矿业</t>
+    <t>维科技术,圣阳股份,雄韬股份,万里股份,豪鹏科技,石大胜华,璞泰来</t>
+  </si>
+  <si>
+    <t>网达软件,云赛智联,星环科技-U,远光软件,拓维信息,延华智能</t>
+  </si>
+  <si>
+    <t>蓝焰控股,中国海油,洲际油气</t>
+  </si>
+  <si>
+    <t>道明光学,唯科科技,佛塑科技,国风新材,乐凯胶片,金发科技,沃顿科技</t>
+  </si>
+  <si>
+    <t>辽宁能源,郑州煤电,兖矿能源,大有能源</t>
+  </si>
+  <si>
+    <t>华宏科技,法尔胜</t>
+  </si>
+  <si>
+    <t>科威尔,科华数据,金时科技,东方电气,奥 特 迅,上海电气,中国动力</t>
+  </si>
+  <si>
+    <t>冠豪高新,荣晟环保,安妮股份</t>
+  </si>
+  <si>
+    <t>云南锗业,翔鹭钨业,华锡有色,东方锆业,锡业股份,中稀有色</t>
+  </si>
+  <si>
+    <t>群兴玩具,舒华体育</t>
+  </si>
+  <si>
+    <t>安徽合力,华东重机,厦工股份,中际联合,长龄液压,南方路机</t>
+  </si>
+  <si>
+    <t>赤峰黄金,晓程科技,招金黄金,四川黄金,西部黄金,湖南黄金</t>
+  </si>
+  <si>
+    <t>云煤能源,安泰集团,陕西黑猫</t>
+  </si>
+  <si>
+    <t>奥康国际,哈森股份,真爱美家,浪莎股份,歌力思</t>
+  </si>
+  <si>
+    <t>可立克,睿能科技,好利科技,京泉华,深圳华强,中电港</t>
+  </si>
+  <si>
+    <t>渤海租赁,中油资本,爱建集团,瑞达期货</t>
+  </si>
+  <si>
+    <t>长光华芯,兆易创新,德明利,华亚智能,佰维存储</t>
+  </si>
+  <si>
+    <t>长城军工,银河电子,光电股份,北方导航</t>
+  </si>
+  <si>
+    <t>江南高纤,健盛集团,孚日股份,云中马</t>
+  </si>
+  <si>
+    <t>宁波建工,浙江建投</t>
+  </si>
+  <si>
+    <t>龙洲股份,福然德,宏川智慧,远大控股,天顺股份</t>
+  </si>
+  <si>
+    <t>新华传媒,中国科传,出版传媒</t>
+  </si>
+  <si>
+    <t>安阳钢铁,酒钢宏兴</t>
   </si>
   <si>
     <t>祥明智能,八方股份,兆威机电</t>
   </si>
   <si>
-    <t>丽岛新材,众源新材,国城矿业</t>
-  </si>
-  <si>
-    <t>中国瑞林,中衡设计,太极实业</t>
-  </si>
-  <si>
-    <t>奥康国际,浪莎股份,歌力思,真爱美家</t>
+    <t>中衡设计,太极实业,中国瑞林</t>
+  </si>
+  <si>
+    <t>南京公用,漳州发展,粤桂股份</t>
+  </si>
+  <si>
+    <t>国城矿业,众源新材,丽岛新材</t>
+  </si>
+  <si>
+    <t>方大炭素,海南矿业,大中矿业</t>
+  </si>
+  <si>
+    <t>福建水泥,韩建河山</t>
+  </si>
+  <si>
+    <t>友邦吊顶,法狮龙,扬子新材</t>
+  </si>
+  <si>
+    <t>日出东方,万和电气</t>
   </si>
   <si>
     <t>德才股份,科新发展</t>
   </si>
   <si>
-    <t>万和电气,日出东方</t>
-  </si>
-  <si>
-    <t>粤桂股份,南京公用</t>
-  </si>
-  <si>
-    <t>中国科传,新华传媒</t>
-  </si>
-  <si>
-    <t>中源协和,万泽股份</t>
+    <t>康盛股份,金海高科,禾盛新材</t>
+  </si>
+  <si>
+    <t>万泽股份,中源协和</t>
+  </si>
+  <si>
+    <t>狮头股份</t>
+  </si>
+  <si>
+    <t>天地在线,三人行</t>
+  </si>
+  <si>
+    <t>融捷股份</t>
+  </si>
+  <si>
+    <t>西王食品</t>
+  </si>
+  <si>
+    <t>必得科技,中国铁物</t>
   </si>
   <si>
     <t>石英股份,联瑞新材</t>
   </si>
   <si>
+    <t>赫美集团,茂业商业</t>
+  </si>
+  <si>
+    <t>海洋王,联域股份</t>
+  </si>
+  <si>
+    <t>华资实业,冠农股份</t>
+  </si>
+  <si>
+    <t>联科科技,黑猫股份</t>
+  </si>
+  <si>
+    <t>深圳新星,福达合金</t>
+  </si>
+  <si>
     <t>莲花控股</t>
   </si>
   <si>
-    <t>联科科技,黑猫股份</t>
+    <t>新日股份,爱玛科技</t>
+  </si>
+  <si>
+    <t>兆驰股份</t>
   </si>
   <si>
     <t>航天彩虹</t>
   </si>
   <si>
-    <t>赫美集团,茂业商业</t>
-  </si>
-  <si>
-    <t>兆驰股份</t>
-  </si>
-  <si>
-    <t>禾盛新材,金海高科</t>
-  </si>
-  <si>
-    <t>爱玛科技,新日股份</t>
-  </si>
-  <si>
-    <t>韩建河山</t>
-  </si>
-  <si>
-    <t>福达合金,深圳新星</t>
-  </si>
-  <si>
-    <t>法狮龙,扬子新材</t>
-  </si>
-  <si>
-    <t>联域股份,海洋王</t>
-  </si>
-  <si>
-    <t>狮头股份</t>
-  </si>
-  <si>
-    <t>融捷股份</t>
+    <t>延江股份</t>
+  </si>
+  <si>
+    <t>桂林旅游</t>
+  </si>
+  <si>
+    <t>中体产业</t>
+  </si>
+  <si>
+    <t>平潭发展</t>
   </si>
   <si>
     <t>贵广网络</t>
   </si>
   <si>
+    <t>京基智农</t>
+  </si>
+  <si>
+    <t>天通股份</t>
+  </si>
+  <si>
+    <t>澳柯玛</t>
+  </si>
+  <si>
+    <t>播恩集团</t>
+  </si>
+  <si>
+    <t>世联行</t>
+  </si>
+  <si>
     <t>海马汽车</t>
   </si>
   <si>
-    <t>京基智农</t>
-  </si>
-  <si>
-    <t>世联行</t>
-  </si>
-  <si>
-    <t>西王食品</t>
-  </si>
-  <si>
-    <t>天通股份</t>
-  </si>
-  <si>
-    <t>澳柯玛</t>
-  </si>
-  <si>
-    <t>天地在线</t>
-  </si>
-  <si>
-    <t>播恩集团</t>
+    <t>塞力医疗</t>
+  </si>
+  <si>
+    <t>顺网科技</t>
+  </si>
+  <si>
+    <t>国际医学</t>
+  </si>
+  <si>
+    <t>常宝股份</t>
+  </si>
+  <si>
+    <t>交运股份</t>
   </si>
   <si>
     <t>彩虹集团</t>
   </si>
   <si>
-    <t>顺网科技</t>
-  </si>
-  <si>
-    <t>国际医学</t>
-  </si>
-  <si>
-    <t>塞力医疗</t>
-  </si>
-  <si>
     <t>行动教育</t>
-  </si>
-  <si>
-    <t>常宝股份</t>
-  </si>
-  <si>
-    <t>交运股份</t>
-  </si>
-  <si>
-    <t>必得科技</t>
   </si>
   <si>
     <t>富临运业</t>
@@ -1335,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1366,22 +1414,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F2">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="G2" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1389,22 +1437,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D3">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1412,68 +1460,68 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="G4" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6">
         <v>40</v>
       </c>
-      <c r="C6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D6">
-        <v>38</v>
-      </c>
       <c r="E6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1481,22 +1529,22 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>20</v>
       </c>
       <c r="F7">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="G7" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1504,68 +1552,68 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D8">
         <v>32</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F8">
         <v>1.6</v>
       </c>
       <c r="G8" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F9">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="G9" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D10">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="G10" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1573,137 +1621,137 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11">
         <v>12</v>
       </c>
       <c r="F11">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="G12" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D13">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="G13" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G14" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F15">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G15" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F16">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G16" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1711,22 +1759,22 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E17">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F17">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G17" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1734,22 +1782,22 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D18">
         <v>17</v>
       </c>
       <c r="E18">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F18">
         <v>0.85</v>
       </c>
       <c r="G18" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1757,10 +1805,10 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D19">
         <v>17</v>
@@ -1772,7 +1820,7 @@
         <v>0.85</v>
       </c>
       <c r="G19" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1780,22 +1828,22 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D20">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G20" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1803,125 +1851,125 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="G21" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E22">
         <v>9</v>
       </c>
       <c r="F22">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G22" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D23">
         <v>14</v>
       </c>
       <c r="E23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23">
         <v>0.7</v>
       </c>
       <c r="G23" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24">
         <v>9</v>
       </c>
       <c r="F24">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="G24" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D25">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25">
         <v>9</v>
       </c>
       <c r="F25">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="G25" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D26">
         <v>13</v>
@@ -1933,7 +1981,7 @@
         <v>0.65</v>
       </c>
       <c r="G26" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1941,137 +1989,137 @@
         <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D27">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="G27" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="G28" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E29">
         <v>8</v>
       </c>
       <c r="F29">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="G29" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G30" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C31" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D31">
         <v>10</v>
       </c>
       <c r="E31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F31">
         <v>0.5</v>
       </c>
       <c r="G31" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E32">
         <v>7</v>
       </c>
       <c r="F32">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="G32" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2079,10 +2127,10 @@
         <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D33">
         <v>9</v>
@@ -2094,30 +2142,30 @@
         <v>0.45</v>
       </c>
       <c r="G33" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C34" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F34">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G34" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2125,10 +2173,10 @@
         <v>14</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D35">
         <v>8</v>
@@ -2140,87 +2188,87 @@
         <v>0.4</v>
       </c>
       <c r="G35" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" t="s">
+        <v>174</v>
+      </c>
+      <c r="D36">
         <v>8</v>
       </c>
-      <c r="B36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" t="s">
-        <v>168</v>
-      </c>
-      <c r="D36">
-        <v>7</v>
-      </c>
       <c r="E36">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="G36" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D37">
+        <v>8</v>
+      </c>
+      <c r="E37">
         <v>7</v>
       </c>
-      <c r="E37">
-        <v>6</v>
-      </c>
       <c r="F37">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="G37" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D38">
         <v>7</v>
       </c>
       <c r="E38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F38">
         <v>0.35</v>
       </c>
       <c r="G38" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D39">
         <v>7</v>
@@ -2232,191 +2280,191 @@
         <v>0.35</v>
       </c>
       <c r="G39" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C40" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F40">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G40" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C41" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F41">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G41" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C42" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D42">
+        <v>7</v>
+      </c>
+      <c r="E42">
         <v>6</v>
       </c>
-      <c r="E42">
-        <v>3</v>
-      </c>
       <c r="F42">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G42" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C43" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="D43">
         <v>6</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43">
         <v>0.3</v>
       </c>
       <c r="G43" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C44" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D44">
         <v>6</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F44">
         <v>0.3</v>
       </c>
       <c r="G44" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C45" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F45">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G45" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C46" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G46" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C47" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="E47">
         <v>5</v>
       </c>
-      <c r="E47">
-        <v>2</v>
-      </c>
       <c r="F47">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G47" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2424,114 +2472,114 @@
         <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C48" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E48">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F48">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G48" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C49" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D49">
         <v>5</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F49">
         <v>0.25</v>
       </c>
       <c r="G49" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C50" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F50">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G50" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C51" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E51">
         <v>4</v>
       </c>
       <c r="F51">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G51" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E52">
         <v>4</v>
       </c>
       <c r="F52">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G52" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2539,45 +2587,45 @@
         <v>18</v>
       </c>
       <c r="B53" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C53" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D53">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G53" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C54" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F54">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="G54" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2585,10 +2633,10 @@
         <v>28</v>
       </c>
       <c r="B55" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C55" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D55">
         <v>4</v>
@@ -2600,41 +2648,41 @@
         <v>0.2</v>
       </c>
       <c r="G55" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C56" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D56">
         <v>4</v>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F56">
         <v>0.2</v>
       </c>
       <c r="G56" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B57" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C57" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D57">
         <v>4</v>
@@ -2646,7 +2694,7 @@
         <v>0.2</v>
       </c>
       <c r="G57" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2654,10 +2702,10 @@
         <v>18</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C58" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D58">
         <v>4</v>
@@ -2669,53 +2717,53 @@
         <v>0.2</v>
       </c>
       <c r="G58" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D59">
         <v>4</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59">
         <v>0.2</v>
       </c>
       <c r="G59" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C60" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60">
         <v>3</v>
       </c>
-      <c r="E60">
-        <v>2</v>
-      </c>
       <c r="F60">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G60" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2723,33 +2771,33 @@
         <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C61" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D61">
+        <v>4</v>
+      </c>
+      <c r="E61">
         <v>3</v>
       </c>
-      <c r="E61">
-        <v>2</v>
-      </c>
       <c r="F61">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G61" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C62" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D62">
         <v>3</v>
@@ -2761,7 +2809,7 @@
         <v>0.15</v>
       </c>
       <c r="G62" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2769,33 +2817,33 @@
         <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C63" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D63">
         <v>3</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63">
         <v>0.15</v>
       </c>
       <c r="G63" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C64" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -2807,30 +2855,30 @@
         <v>0.15</v>
       </c>
       <c r="G64" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B65" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C65" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65">
         <v>2</v>
       </c>
       <c r="F65">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G65" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2838,56 +2886,56 @@
         <v>32</v>
       </c>
       <c r="B66" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C66" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G66" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B67" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C67" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67">
         <v>2</v>
       </c>
       <c r="F67">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G67" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C68" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -2899,18 +2947,18 @@
         <v>0.1</v>
       </c>
       <c r="G68" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B69" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C69" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -2922,18 +2970,18 @@
         <v>0.1</v>
       </c>
       <c r="G69" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C70" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -2945,41 +2993,41 @@
         <v>0.1</v>
       </c>
       <c r="G70" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B71" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C71" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D71">
         <v>2</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71">
         <v>0.1</v>
       </c>
       <c r="G71" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C72" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -2991,41 +3039,41 @@
         <v>0.1</v>
       </c>
       <c r="G72" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C73" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D73">
         <v>2</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73">
         <v>0.1</v>
       </c>
       <c r="G73" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B74" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C74" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -3037,18 +3085,18 @@
         <v>0.1</v>
       </c>
       <c r="G74" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C75" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -3060,18 +3108,18 @@
         <v>0.1</v>
       </c>
       <c r="G75" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B76" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C76" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -3083,156 +3131,156 @@
         <v>0.1</v>
       </c>
       <c r="G76" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C77" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G77" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C78" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G78" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B79" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C79" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G79" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B80" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C80" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G80" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B81" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C81" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81">
         <v>1</v>
       </c>
       <c r="F81">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G81" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B82" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C82" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G82" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B83" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C83" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3244,18 +3292,18 @@
         <v>0.05</v>
       </c>
       <c r="G83" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B84" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C84" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3267,18 +3315,18 @@
         <v>0.05</v>
       </c>
       <c r="G84" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B85" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C85" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3290,18 +3338,18 @@
         <v>0.05</v>
       </c>
       <c r="G85" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B86" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C86" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3313,18 +3361,18 @@
         <v>0.05</v>
       </c>
       <c r="G86" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B87" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C87" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3336,18 +3384,18 @@
         <v>0.05</v>
       </c>
       <c r="G87" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B88" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C88" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3359,18 +3407,18 @@
         <v>0.05</v>
       </c>
       <c r="G88" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C89" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3382,18 +3430,18 @@
         <v>0.05</v>
       </c>
       <c r="G89" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B90" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C90" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3405,18 +3453,18 @@
         <v>0.05</v>
       </c>
       <c r="G90" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B91" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C91" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3428,18 +3476,18 @@
         <v>0.05</v>
       </c>
       <c r="G91" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B92" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C92" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3451,18 +3499,18 @@
         <v>0.05</v>
       </c>
       <c r="G92" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B93" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C93" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3474,18 +3522,18 @@
         <v>0.05</v>
       </c>
       <c r="G93" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B94" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C94" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3497,18 +3545,18 @@
         <v>0.05</v>
       </c>
       <c r="G94" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B95" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C95" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3520,18 +3568,18 @@
         <v>0.05</v>
       </c>
       <c r="G95" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B96" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C96" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3543,18 +3591,18 @@
         <v>0.05</v>
       </c>
       <c r="G96" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B97" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C97" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3566,18 +3614,18 @@
         <v>0.05</v>
       </c>
       <c r="G97" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B98" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C98" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3589,18 +3637,18 @@
         <v>0.05</v>
       </c>
       <c r="G98" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B99" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C99" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3612,7 +3660,122 @@
         <v>0.05</v>
       </c>
       <c r="G99" t="s">
-        <v>329</v>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
+        <v>36</v>
+      </c>
+      <c r="B100" t="s">
+        <v>135</v>
+      </c>
+      <c r="C100" t="s">
+        <v>238</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+      <c r="F100">
+        <v>0.05</v>
+      </c>
+      <c r="G100" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
+        <v>17</v>
+      </c>
+      <c r="B101" t="s">
+        <v>136</v>
+      </c>
+      <c r="C101" t="s">
+        <v>239</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101">
+        <v>0.05</v>
+      </c>
+      <c r="G101" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
+        <v>9</v>
+      </c>
+      <c r="B102" t="s">
+        <v>137</v>
+      </c>
+      <c r="C102" t="s">
+        <v>240</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102">
+        <v>0.05</v>
+      </c>
+      <c r="G102" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" t="s">
+        <v>19</v>
+      </c>
+      <c r="B103" t="s">
+        <v>138</v>
+      </c>
+      <c r="C103" t="s">
+        <v>241</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+      <c r="F103">
+        <v>0.05</v>
+      </c>
+      <c r="G103" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
+        <v>22</v>
+      </c>
+      <c r="B104" t="s">
+        <v>139</v>
+      </c>
+      <c r="C104" t="s">
+        <v>242</v>
+      </c>
+      <c r="D104">
+        <v>1</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+      <c r="F104">
+        <v>0.05</v>
+      </c>
+      <c r="G104" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>
